--- a/Versão5/PRO/Ontologia_Cromatica.xlsx
+++ b/Versão5/PRO/Ontologia_Cromatica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CROM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654A4936-4477-4761-BF44-47B722367C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0351B6A-4C05-4687-BC0B-D019DA1E8289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="394">
   <si>
     <t>Key</t>
   </si>
@@ -2002,12 +2002,6 @@
     <t>Cores do catálogo Departamento Nacional de Infraestrutura de Transportes do Brasil.</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -2303,6 +2297,150 @@
   </si>
   <si>
     <t>Paletas</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cor</t>
+  </si>
+  <si>
+    <t>Cromático</t>
+  </si>
+  <si>
+    <t>Cores</t>
+  </si>
+  <si>
+    <t>Paletas.Usadas</t>
+  </si>
+  <si>
+    <t>Cor utilizada no projeto.</t>
+  </si>
+  <si>
+    <t>Amount of cyan color that can vary between 0 and 255.</t>
+  </si>
+  <si>
+    <t>Amount of magenta color that can vary between 0 and 255.</t>
+  </si>
+  <si>
+    <t>Amount of yellow color between which can vary from 0 to 255.</t>
+  </si>
+  <si>
+    <t>Amount of black color between which can vary from 0 to 255.</t>
+  </si>
+  <si>
+    <t>Amount of red color that can vary between 0 and 255.</t>
+  </si>
+  <si>
+    <t>Amount of green color between that can vary from 0 to 255.</t>
+  </si>
+  <si>
+    <t>Amount of blue color between that can vary from 0 to 255.</t>
+  </si>
+  <si>
+    <t>Amount of transparency that can vary between 0 and 255.</t>
+  </si>
+  <si>
+    <t>Digital color composed of CMY channels.</t>
+  </si>
+  <si>
+    <t>Digital color composed of CMYB channels.</t>
+  </si>
+  <si>
+    <t>Digital color composed of RGB channels.</t>
+  </si>
+  <si>
+    <t>Digital color composed of RGBA channels. Channel A defines transparency.</t>
+  </si>
+  <si>
+    <t>Munsell Color System: Hue Parameter.</t>
+  </si>
+  <si>
+    <t>Munsell color system: Luminosity parameter.</t>
+  </si>
+  <si>
+    <t>Munsell Color System: Croma Parameter. It is the degree of distance of a color from the neutral color of the same value. A low chroma weakens the color. A high chroma for saturated, strong, or vivid color.</t>
+  </si>
+  <si>
+    <t>Munsell system-specific color.</t>
+  </si>
+  <si>
+    <t>Specific color from the Pantone catalog.</t>
+  </si>
+  <si>
+    <t>Colors from the catalog of the National Department of Transport Infrastructure of Brazil.</t>
+  </si>
+  <si>
+    <t>Color used in the project.</t>
+  </si>
+  <si>
+    <t>Cantidad de color cian que puede variar entre 0 y 255.</t>
+  </si>
+  <si>
+    <t>Cantidad de color magenta que puede variar entre 0 y 255.</t>
+  </si>
+  <si>
+    <t>La cantidad de color amarillo entre los cuales puede variar de 0 a 255.</t>
+  </si>
+  <si>
+    <t>La cantidad de color negro entre ellos puede variar de 0 a 255.</t>
+  </si>
+  <si>
+    <t>Cantidad de color rojo que puede variar entre 0 y 255.</t>
+  </si>
+  <si>
+    <t>La cantidad de color verde entre eso puede variar de 0 a 255.</t>
+  </si>
+  <si>
+    <t>La cantidad de color azul entre eso puede variar de 0 a 255.</t>
+  </si>
+  <si>
+    <t>Cantidad de transparencia que puede variar entre 0 y 255.</t>
+  </si>
+  <si>
+    <t>Color digital compuesto por canales CMY.</t>
+  </si>
+  <si>
+    <t>Color digital compuesto por canales CMYB.</t>
+  </si>
+  <si>
+    <t>Color digital compuesto por canales RGB.</t>
+  </si>
+  <si>
+    <t>Color digital compuesto por canales RGBA. El Canal A define transparencia.</t>
+  </si>
+  <si>
+    <t>Sistema de color Munsell: Parámetro de tono.</t>
+  </si>
+  <si>
+    <t>Sistema de color Munsell: Parámetro de luminosidad.</t>
+  </si>
+  <si>
+    <t>Sistema de color Munsell: Parámetro Croma. Es el grado de distancia de un color al color neutro del mismo valor. Un cromo bajo debilita el color. Un alto nivel de cromancia para colores saturados, intensos o vivos.</t>
+  </si>
+  <si>
+    <t>Color específico del sistema Munsell.</t>
+  </si>
+  <si>
+    <t>Color específico del catálogo de Pantone.</t>
+  </si>
+  <si>
+    <t>Colores del catálogo del Departamento Nacional de Infraestructuras de Transporte de Brasil.</t>
+  </si>
+  <si>
+    <t>Color usado en el proyecto.</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
   </si>
   <si>
     <t>[ - ]</t>
@@ -2675,7 +2813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2904,11 +3042,17 @@
     <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -2997,6 +3141,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3004,6 +3156,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3338,15 +3508,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3354,10 +3524,10 @@
         <v>50</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3365,10 +3535,10 @@
         <v>76</v>
       </c>
       <c r="C2" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3376,10 +3546,10 @@
         <v>98</v>
       </c>
       <c r="C3" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3387,10 +3557,10 @@
         <v>62</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3399,10 +3569,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3411,10 +3581,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3422,21 +3592,21 @@
         <v>63</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="61" t="s">
         <v>251</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3444,10 +3614,10 @@
         <v>65</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3455,10 +3625,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3466,10 +3636,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3477,10 +3647,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3488,10 +3658,10 @@
         <v>38</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3499,10 +3669,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3510,10 +3680,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3521,10 +3691,10 @@
         <v>38</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3532,57 +3702,57 @@
         <v>99</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46244.600059259261</v>
+        <v>46253.797543171298</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B20" s="63" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B21" s="63" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3590,10 +3760,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3601,10 +3771,10 @@
         <v>38</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3612,10 +3782,10 @@
         <v>100</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3623,19 +3793,19 @@
         <v>101</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of chromatic elements</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3645,36 +3815,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC20"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="108.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="110.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.42578125" style="70" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.7109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="70" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7" style="70" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="109" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="79.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="82.921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="79.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.69140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6" style="70" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.3828125" style="70" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6" style="70" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.69140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6" style="70" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.3046875" style="70" customWidth="1"/>
+    <col min="27" max="27" width="4.921875" style="70" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.07421875" style="70" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3" style="70" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
@@ -3726,52 +3898,58 @@
       <c r="Q1" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="24" t="s">
+      <c r="U1" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="V1" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="V1" s="24" t="s">
+      <c r="W1" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="76" t="s">
+      <c r="X1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="24" t="s">
+      <c r="Y1" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="Z1" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="AA1" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="AB1" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="AC1" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="Y1" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z1" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="AA1" s="59" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="64">
         <v>2</v>
       </c>
       <c r="B2" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E2" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>124</v>
@@ -3789,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="74" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L2" s="66" t="str">
         <f>_xlfn.CONCAT(C2)</f>
@@ -3810,61 +3988,65 @@
       <c r="P2" s="66" t="s">
         <v>241</v>
       </c>
-      <c r="Q2" s="66" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Cantidad de color cian que puede variar entre 0 y 255.</v>
-      </c>
-      <c r="R2" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="60" t="str">
-        <f t="shared" ref="S2:U17" si="1">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="Q2" s="66" t="s">
+        <v>370</v>
+      </c>
+      <c r="R2" s="60" t="s">
+        <v>351</v>
+      </c>
+      <c r="S2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="60" t="str">
+        <f t="shared" ref="T2:V17" si="1">SUBSTITUTE(C2, "_", " ")</f>
         <v>Cromáticos</v>
       </c>
-      <c r="T2" s="60" t="str">
+      <c r="U2" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U2" s="65" t="str">
+      <c r="V2" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V2" s="60" t="s">
+      <c r="W2" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="77" t="str">
-        <f t="shared" ref="W2:W19" si="2">CONCATENATE("Key-CROMA-",A2)</f>
+      <c r="X2" s="77" t="str">
+        <f t="shared" ref="X2:X20" si="2">CONCATENATE("Key-CROMA-",A2)</f>
         <v>Key-CROMA-2</v>
       </c>
-      <c r="X2" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y2" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z2" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA2" s="60" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Amount of cyan color that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB2" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC2" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="64">
         <v>3</v>
       </c>
       <c r="B3" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E3" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F3" s="26" t="s">
         <v>123</v>
@@ -3882,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="74" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L3" s="66" t="str">
         <f>_xlfn.CONCAT(C3)</f>
@@ -3903,61 +4085,65 @@
       <c r="P3" s="66" t="s">
         <v>240</v>
       </c>
-      <c r="Q3" s="66" t="str">
-        <f t="shared" ref="Q3:Q19" si="3">_xlfn.TRANSLATE(P3,"pt","es")</f>
-        <v>Cantidad de color magenta que puede variar entre 0 y 255.</v>
-      </c>
-      <c r="R3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="60" t="str">
+      <c r="Q3" s="66" t="s">
+        <v>371</v>
+      </c>
+      <c r="R3" s="60" t="s">
+        <v>352</v>
+      </c>
+      <c r="S3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T3" s="60" t="str">
+      <c r="U3" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U3" s="65" t="str">
+      <c r="V3" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V3" s="60" t="s">
+      <c r="W3" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="77" t="str">
+      <c r="X3" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-3</v>
       </c>
-      <c r="X3" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y3" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z3" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA3" s="60" t="str">
-        <f t="shared" ref="AA3:AA19" si="4">_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Amount of magenta color that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA3" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB3" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC3" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="64">
         <v>4</v>
       </c>
       <c r="B4" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C4" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E4" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F4" s="26" t="s">
         <v>125</v>
@@ -3975,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="74" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L4" s="66" t="str">
         <f>_xlfn.CONCAT(C4)</f>
@@ -3996,61 +4182,65 @@
       <c r="P4" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="Q4" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>La cantidad de color amarillo entre los cuales puede variar de 0 a 255.</v>
-      </c>
-      <c r="R4" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="60" t="str">
+      <c r="Q4" s="66" t="s">
+        <v>372</v>
+      </c>
+      <c r="R4" s="60" t="s">
+        <v>353</v>
+      </c>
+      <c r="S4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T4" s="60" t="str">
+      <c r="U4" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U4" s="65" t="str">
+      <c r="V4" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V4" s="60" t="s">
+      <c r="W4" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="77" t="str">
+      <c r="X4" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-4</v>
       </c>
-      <c r="X4" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y4" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z4" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA4" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Amount of yellow color between which can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA4" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB4" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC4" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="64">
         <v>5</v>
       </c>
       <c r="B5" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E5" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F5" s="26" t="s">
         <v>126</v>
@@ -4068,10 +4258,10 @@
         <v>1</v>
       </c>
       <c r="K5" s="74" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L5" s="66" t="str">
-        <f t="shared" ref="L5:L19" si="5">_xlfn.CONCAT(C5)</f>
+        <f t="shared" ref="L5:L20" si="3">_xlfn.CONCAT(C5)</f>
         <v>Cromáticos</v>
       </c>
       <c r="M5" s="66" t="str">
@@ -4089,61 +4279,65 @@
       <c r="P5" s="66" t="s">
         <v>242</v>
       </c>
-      <c r="Q5" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>La cantidad de color negro entre ellos puede variar de 0 a 255.</v>
-      </c>
-      <c r="R5" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="60" t="str">
+      <c r="Q5" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="R5" s="60" t="s">
+        <v>354</v>
+      </c>
+      <c r="S5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T5" s="60" t="str">
+      <c r="U5" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U5" s="65" t="str">
+      <c r="V5" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V5" s="60" t="s">
+      <c r="W5" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W5" s="77" t="str">
+      <c r="X5" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-5</v>
       </c>
-      <c r="X5" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y5" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z5" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA5" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Amount of black color between which can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA5" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB5" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC5" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="64">
         <v>6</v>
       </c>
       <c r="B6" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E6" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F6" s="26" t="s">
         <v>93</v>
@@ -4161,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="74" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L6" s="66" t="str">
         <f>_xlfn.CONCAT(C6)</f>
@@ -4182,61 +4376,65 @@
       <c r="P6" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="Q6" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Cantidad de color rojo que puede variar entre 0 y 255.</v>
-      </c>
-      <c r="R6" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="60" t="str">
+      <c r="Q6" s="66" t="s">
+        <v>374</v>
+      </c>
+      <c r="R6" s="60" t="s">
+        <v>355</v>
+      </c>
+      <c r="S6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T6" s="60" t="str">
+      <c r="U6" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U6" s="65" t="str">
+      <c r="V6" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V6" s="60" t="s">
+      <c r="W6" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W6" s="77" t="str">
+      <c r="X6" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-6</v>
       </c>
-      <c r="X6" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y6" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z6" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA6" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Amount of red color that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA6" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB6" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC6" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="64">
         <v>7</v>
       </c>
       <c r="B7" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E7" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F7" s="26" t="s">
         <v>94</v>
@@ -4254,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="74" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L7" s="66" t="str">
         <f>_xlfn.CONCAT(C7)</f>
@@ -4275,61 +4473,65 @@
       <c r="P7" s="66" t="s">
         <v>243</v>
       </c>
-      <c r="Q7" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>La cantidad de color verde entre eso puede variar de 0 a 255.</v>
-      </c>
-      <c r="R7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="60" t="str">
+      <c r="Q7" s="66" t="s">
+        <v>375</v>
+      </c>
+      <c r="R7" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="S7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T7" s="60" t="str">
+      <c r="U7" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U7" s="65" t="str">
+      <c r="V7" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V7" s="60" t="s">
+      <c r="W7" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W7" s="77" t="str">
+      <c r="X7" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-7</v>
       </c>
-      <c r="X7" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y7" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z7" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA7" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Amount of green color between that can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA7" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB7" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC7" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="64">
         <v>8</v>
       </c>
       <c r="B8" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E8" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F8" s="26" t="s">
         <v>95</v>
@@ -4347,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="74" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L8" s="66" t="str">
         <f>_xlfn.CONCAT(C8)</f>
@@ -4368,61 +4570,65 @@
       <c r="P8" s="66" t="s">
         <v>237</v>
       </c>
-      <c r="Q8" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>La cantidad de color azul entre eso puede variar de 0 a 255.</v>
-      </c>
-      <c r="R8" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="60" t="str">
+      <c r="Q8" s="66" t="s">
+        <v>376</v>
+      </c>
+      <c r="R8" s="60" t="s">
+        <v>357</v>
+      </c>
+      <c r="S8" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T8" s="60" t="str">
+      <c r="U8" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U8" s="65" t="str">
+      <c r="V8" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V8" s="60" t="s">
+      <c r="W8" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W8" s="77" t="str">
+      <c r="X8" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-8</v>
       </c>
-      <c r="X8" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y8" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z8" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA8" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Amount of blue color between that can vary from 0 to 255.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA8" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB8" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC8" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="64">
         <v>9</v>
       </c>
       <c r="B9" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="E9" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F9" s="26" t="s">
         <v>96</v>
@@ -4440,10 +4646,10 @@
         <v>1</v>
       </c>
       <c r="K9" s="74" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L9" s="66" t="str">
-        <f t="shared" ref="L9:L11" si="6">_xlfn.CONCAT(C9)</f>
+        <f t="shared" ref="L9:L11" si="4">_xlfn.CONCAT(C9)</f>
         <v>Cromáticos</v>
       </c>
       <c r="M9" s="66" t="str">
@@ -4461,58 +4667,62 @@
       <c r="P9" s="66" t="s">
         <v>244</v>
       </c>
-      <c r="Q9" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Cantidad de transparencia que puede variar entre 0 y 255.</v>
-      </c>
-      <c r="R9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="60" t="str">
+      <c r="Q9" s="66" t="s">
+        <v>377</v>
+      </c>
+      <c r="R9" s="60" t="s">
+        <v>358</v>
+      </c>
+      <c r="S9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T9" s="60" t="str">
+      <c r="U9" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U9" s="65" t="str">
+      <c r="V9" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Canal.de.Cor</v>
       </c>
-      <c r="V9" s="60" t="s">
+      <c r="W9" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W9" s="77" t="str">
+      <c r="X9" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-9</v>
       </c>
-      <c r="X9" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y9" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z9" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA9" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Amount of transparency that can vary between 0 and 255.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA9" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB9" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC9" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="64">
         <v>10</v>
       </c>
       <c r="B10" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E10" s="43" t="s">
         <v>97</v>
@@ -4533,10 +4743,10 @@
         <v>1</v>
       </c>
       <c r="K10" s="75" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L10" s="67" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Cromáticos</v>
       </c>
       <c r="M10" s="67" t="str">
@@ -4554,58 +4764,62 @@
       <c r="P10" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="Q10" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Color digital compuesto por canales CMY.</v>
-      </c>
-      <c r="R10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="60" t="str">
+      <c r="Q10" s="66" t="s">
+        <v>378</v>
+      </c>
+      <c r="R10" s="60" t="s">
+        <v>359</v>
+      </c>
+      <c r="S10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T10" s="60" t="str">
+      <c r="U10" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U10" s="65" t="str">
+      <c r="V10" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Cor.Digital</v>
       </c>
-      <c r="V10" s="60" t="s">
+      <c r="W10" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W10" s="77" t="str">
+      <c r="X10" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-10</v>
       </c>
-      <c r="X10" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y10" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z10" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA10" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Digital color composed of CMY channels.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA10" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB10" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC10" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="64">
         <v>11</v>
       </c>
       <c r="B11" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E11" s="43" t="s">
         <v>97</v>
@@ -4626,10 +4840,10 @@
         <v>1</v>
       </c>
       <c r="K11" s="75" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L11" s="67" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Cromáticos</v>
       </c>
       <c r="M11" s="67" t="str">
@@ -4647,58 +4861,62 @@
       <c r="P11" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="Q11" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Color digital compuesto por canales CMYB.</v>
-      </c>
-      <c r="R11" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="60" t="str">
+      <c r="Q11" s="66" t="s">
+        <v>379</v>
+      </c>
+      <c r="R11" s="60" t="s">
+        <v>360</v>
+      </c>
+      <c r="S11" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T11" s="60" t="str">
+      <c r="U11" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U11" s="65" t="str">
+      <c r="V11" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Cor.Digital</v>
       </c>
-      <c r="V11" s="60" t="s">
+      <c r="W11" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W11" s="77" t="str">
+      <c r="X11" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-11</v>
       </c>
-      <c r="X11" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y11" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z11" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA11" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Digital color composed of CMYB channels.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA11" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB11" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC11" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="64">
         <v>12</v>
       </c>
       <c r="B12" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E12" s="43" t="s">
         <v>97</v>
@@ -4719,10 +4937,10 @@
         <v>1</v>
       </c>
       <c r="K12" s="75" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L12" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Cromáticos</v>
       </c>
       <c r="M12" s="67" t="str">
@@ -4740,58 +4958,62 @@
       <c r="P12" s="67" t="s">
         <v>234</v>
       </c>
-      <c r="Q12" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Color digital compuesto por canales RGB.</v>
-      </c>
-      <c r="R12" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="60" t="str">
+      <c r="Q12" s="66" t="s">
+        <v>380</v>
+      </c>
+      <c r="R12" s="60" t="s">
+        <v>361</v>
+      </c>
+      <c r="S12" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T12" s="60" t="str">
+      <c r="U12" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U12" s="65" t="str">
+      <c r="V12" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Cor.Digital</v>
       </c>
-      <c r="V12" s="60" t="s">
+      <c r="W12" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W12" s="77" t="str">
+      <c r="X12" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-12</v>
       </c>
-      <c r="X12" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y12" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z12" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA12" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Digital color composed of RGB channels.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA12" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB12" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC12" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="64">
         <v>13</v>
       </c>
       <c r="B13" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E13" s="43" t="s">
         <v>97</v>
@@ -4812,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="K13" s="75" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L13" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Cromáticos</v>
       </c>
       <c r="M13" s="67" t="str">
@@ -4833,58 +5055,62 @@
       <c r="P13" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="Q13" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Color digital compuesto por canales RGBA. El Canal A define transparencia.</v>
-      </c>
-      <c r="R13" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="60" t="str">
+      <c r="Q13" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="R13" s="60" t="s">
+        <v>362</v>
+      </c>
+      <c r="S13" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T13" s="60" t="str">
+      <c r="U13" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U13" s="65" t="str">
+      <c r="V13" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Cor.Digital</v>
       </c>
-      <c r="V13" s="60" t="s">
+      <c r="W13" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W13" s="77" t="str">
+      <c r="X13" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-13</v>
       </c>
-      <c r="X13" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y13" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z13" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA13" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Digital color composed of RGBA channels. Channel A defines transparency.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA13" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB13" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC13" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="64">
         <v>14</v>
       </c>
       <c r="B14" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>149</v>
@@ -4908,7 +5134,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Cromáticos</v>
       </c>
       <c r="M14" s="67" t="str">
@@ -4926,58 +5152,62 @@
       <c r="P14" s="67" t="s">
         <v>233</v>
       </c>
-      <c r="Q14" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema de color Munsell: Parámetro de tono.</v>
-      </c>
-      <c r="R14" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="60" t="str">
+      <c r="Q14" s="66" t="s">
+        <v>382</v>
+      </c>
+      <c r="R14" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="S14" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T14" s="60" t="str">
+      <c r="U14" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U14" s="65" t="str">
+      <c r="V14" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Munsell</v>
       </c>
-      <c r="V14" s="60" t="s">
+      <c r="W14" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W14" s="77" t="str">
+      <c r="X14" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-14</v>
       </c>
-      <c r="X14" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y14" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z14" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA14" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Munsell Color System: Hue Parameter.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA14" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB14" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC14" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="64">
         <v>15</v>
       </c>
       <c r="B15" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E15" s="43" t="s">
         <v>149</v>
@@ -5001,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Cromáticos</v>
       </c>
       <c r="M15" s="67" t="str">
@@ -5019,58 +5249,62 @@
       <c r="P15" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="Q15" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema de color Munsell: Parámetro de luminosidad.</v>
-      </c>
-      <c r="R15" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="60" t="str">
+      <c r="Q15" s="66" t="s">
+        <v>383</v>
+      </c>
+      <c r="R15" s="60" t="s">
+        <v>364</v>
+      </c>
+      <c r="S15" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T15" s="60" t="str">
+      <c r="U15" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U15" s="65" t="str">
+      <c r="V15" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Munsell</v>
       </c>
-      <c r="V15" s="60" t="s">
+      <c r="W15" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W15" s="77" t="str">
+      <c r="X15" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-15</v>
       </c>
-      <c r="X15" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y15" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z15" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA15" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Munsell color system: Luminosity parameter.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA15" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB15" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC15" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="64">
         <v>16</v>
       </c>
       <c r="B16" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D16" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E16" s="43" t="s">
         <v>149</v>
@@ -5094,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Cromáticos</v>
       </c>
       <c r="M16" s="67" t="str">
@@ -5112,58 +5346,62 @@
       <c r="P16" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="Q16" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema de color Munsell: Parámetro Croma. Es el grado de distancia de un color al color neutro del mismo valor. Un cromo bajo debilita el color. Un alto nivel de cromancia para colores saturados, intensos o vivos.</v>
-      </c>
-      <c r="R16" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="60" t="str">
+      <c r="Q16" s="66" t="s">
+        <v>384</v>
+      </c>
+      <c r="R16" s="60" t="s">
+        <v>365</v>
+      </c>
+      <c r="S16" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T16" s="60" t="str">
+      <c r="U16" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U16" s="65" t="str">
+      <c r="V16" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Munsell</v>
       </c>
-      <c r="V16" s="60" t="s">
+      <c r="W16" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W16" s="77" t="str">
+      <c r="X16" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-16</v>
       </c>
-      <c r="X16" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y16" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z16" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA16" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Munsell Color System: Croma Parameter. It is the degree of distance of a color from the neutral color of the same value. A low chroma weakens the color. A high chroma for saturated, strong, or vivid color.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA16" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB16" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC16" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="64">
         <v>17</v>
       </c>
       <c r="B17" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D17" s="28" t="s">
         <v>344</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>346</v>
       </c>
       <c r="E17" s="43" t="s">
         <v>149</v>
@@ -5187,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Cromáticos</v>
       </c>
       <c r="M17" s="67" t="str">
@@ -5205,55 +5443,59 @@
       <c r="P17" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="Q17" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Color específico del sistema Munsell.</v>
-      </c>
-      <c r="R17" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="60" t="str">
+      <c r="Q17" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="R17" s="60" t="s">
+        <v>366</v>
+      </c>
+      <c r="S17" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T17" s="60" t="str">
+      <c r="U17" s="60" t="str">
         <f t="shared" si="1"/>
         <v>Paletas</v>
       </c>
-      <c r="U17" s="65" t="str">
+      <c r="V17" s="65" t="str">
         <f t="shared" si="1"/>
         <v>Munsell</v>
       </c>
-      <c r="V17" s="60" t="s">
+      <c r="W17" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W17" s="77" t="str">
+      <c r="X17" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-17</v>
       </c>
-      <c r="X17" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y17" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z17" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA17" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Munsell system-specific color.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA17" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB17" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC17" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="64">
         <v>18</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D18" s="43" t="s">
         <v>119</v>
@@ -5280,73 +5522,77 @@
         <v>1</v>
       </c>
       <c r="L18" s="67" t="str">
+        <f t="shared" si="3"/>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M18" s="67" t="str">
+        <f t="shared" ref="M18:O20" si="5">_xlfn.CONCAT("", D18)</f>
+        <v>Catálogo</v>
+      </c>
+      <c r="N18" s="67" t="str">
         <f t="shared" si="5"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M18" s="67" t="str">
-        <f t="shared" ref="M18:O19" si="7">_xlfn.CONCAT("", D18)</f>
-        <v>Catálogo</v>
-      </c>
-      <c r="N18" s="67" t="str">
-        <f t="shared" si="7"/>
         <v>Pantone</v>
       </c>
       <c r="O18" s="67" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Cor.Pantone </v>
       </c>
       <c r="P18" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="Q18" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Color específico del catálogo de Pantone.</v>
-      </c>
-      <c r="R18" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="60" t="str">
-        <f t="shared" ref="S18:U19" si="8">SUBSTITUTE(C18, "_", " ")</f>
+      <c r="Q18" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="R18" s="60" t="s">
+        <v>367</v>
+      </c>
+      <c r="S18" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="60" t="str">
+        <f t="shared" ref="T18:V20" si="6">SUBSTITUTE(C18, "_", " ")</f>
         <v>Cromáticos</v>
       </c>
-      <c r="T18" s="60" t="str">
-        <f t="shared" si="8"/>
+      <c r="U18" s="60" t="str">
+        <f t="shared" si="6"/>
         <v>Catálogo</v>
       </c>
-      <c r="U18" s="65" t="str">
-        <f t="shared" si="8"/>
+      <c r="V18" s="65" t="str">
+        <f t="shared" si="6"/>
         <v>Pantone</v>
       </c>
-      <c r="V18" s="60" t="s">
+      <c r="W18" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W18" s="77" t="str">
+      <c r="X18" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-18</v>
       </c>
-      <c r="X18" s="60" t="s">
-        <v>347</v>
-      </c>
       <c r="Y18" s="60" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="Z18" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA18" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Specific color from the Pantone catalog.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="AA18" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB18" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC18" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="64">
         <v>19</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D19" s="43" t="s">
         <v>119</v>
@@ -5373,101 +5619,218 @@
         <v>1</v>
       </c>
       <c r="L19" s="67" t="str">
+        <f t="shared" si="3"/>
+        <v>Cromáticos</v>
+      </c>
+      <c r="M19" s="67" t="str">
         <f t="shared" si="5"/>
-        <v>Cromáticos</v>
-      </c>
-      <c r="M19" s="67" t="str">
-        <f t="shared" si="7"/>
         <v>Catálogo</v>
       </c>
       <c r="N19" s="67" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>DNIT</v>
       </c>
       <c r="O19" s="67" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Cor.Dnit </v>
       </c>
       <c r="P19" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="Q19" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>Colores del catálogo del Departamento Nacional de Infraestructuras de Transporte de Brasil.</v>
-      </c>
-      <c r="R19" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="60" t="str">
-        <f t="shared" si="8"/>
+      <c r="Q19" s="66" t="s">
+        <v>387</v>
+      </c>
+      <c r="R19" s="60" t="s">
+        <v>368</v>
+      </c>
+      <c r="S19" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="60" t="str">
+        <f t="shared" si="6"/>
         <v>Cromáticos</v>
       </c>
-      <c r="T19" s="60" t="str">
-        <f t="shared" si="8"/>
+      <c r="U19" s="60" t="str">
+        <f t="shared" si="6"/>
         <v>Catálogo</v>
       </c>
-      <c r="U19" s="65" t="str">
-        <f t="shared" si="8"/>
+      <c r="V19" s="65" t="str">
+        <f t="shared" si="6"/>
         <v>DNIT</v>
       </c>
-      <c r="V19" s="60" t="s">
+      <c r="W19" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="W19" s="77" t="str">
+      <c r="X19" s="77" t="str">
         <f t="shared" si="2"/>
         <v>Key-CROMA-19</v>
       </c>
-      <c r="X19" s="60" t="s">
+      <c r="Y19" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="Z19" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AA19" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB19" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC19" s="60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="78">
+        <v>20</v>
+      </c>
+      <c r="B20" s="71" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" s="79" t="s">
         <v>347</v>
       </c>
-      <c r="Y19" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="Z19" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA19" s="60" t="str">
-        <f t="shared" si="4"/>
-        <v>Colors from the catalog of the National Department of Transport Infrastructure of Brazil.</v>
+      <c r="D20" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E20" s="79" t="s">
+        <v>348</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="G20" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="67" t="str">
+        <f t="shared" si="3"/>
+        <v>Cromático</v>
+      </c>
+      <c r="M20" s="67" t="str">
+        <f t="shared" si="5"/>
+        <v>Paletas.Usadas</v>
+      </c>
+      <c r="N20" s="67" t="str">
+        <f t="shared" si="5"/>
+        <v>Cores</v>
+      </c>
+      <c r="O20" s="67" t="str">
+        <f t="shared" si="5"/>
+        <v>Cor</v>
+      </c>
+      <c r="P20" s="67" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q20" s="67" t="s">
+        <v>388</v>
+      </c>
+      <c r="R20" s="66" t="s">
+        <v>369</v>
+      </c>
+      <c r="S20" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="60" t="str">
+        <f t="shared" si="6"/>
+        <v>Cromático</v>
+      </c>
+      <c r="U20" s="60" t="str">
+        <f t="shared" si="6"/>
+        <v>Paletas.Usadas</v>
+      </c>
+      <c r="V20" s="65" t="str">
+        <f t="shared" si="6"/>
+        <v>Cores</v>
+      </c>
+      <c r="W20" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="X20" s="77" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-CROMA-20</v>
+      </c>
+      <c r="Y20" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="Z20" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AA20" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB20" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC20" s="60" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA1:AA19 A2:B19">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B20 W20">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:J1 C2:F19 S1:Z1 L2:Q19 S2:V19">
-    <cfRule type="cellIs" dxfId="11" priority="22" operator="equal">
+  <conditionalFormatting sqref="A1:J1 C2:F19 L2:Q19 T2:W19 T1:AC1">
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F19 F21:F1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q1 K2:K13">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R19">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="39" t="s">
         <v>22</v>
       </c>
@@ -5532,7 +5895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="39">
         <v>2</v>
       </c>
@@ -5612,14 +5975,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="36">
         <v>1</v>
       </c>
@@ -5630,7 +5993,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5654,33 +6017,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" style="46" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.15234375" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.69140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.84375" style="46" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="91.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.69140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.15234375" style="41" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.15234375" style="42" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.84375" style="42" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.3046875" style="42" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="91.3828125" style="42" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5" style="42" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.15234375" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="49" t="s">
         <v>91</v>
       </c>
@@ -5751,7 +6114,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -5771,13 +6134,13 @@
         <v>122</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J2" s="57" t="s">
         <v>1</v>
@@ -5789,10 +6152,10 @@
         <v>140</v>
       </c>
       <c r="M2" s="47" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N2" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O2" s="47">
         <v>255</v>
@@ -5823,7 +6186,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="31">
         <v>3</v>
       </c>
@@ -5843,13 +6206,13 @@
         <v>122</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J3" s="57" t="s">
         <v>1</v>
@@ -5861,10 +6224,10 @@
         <v>140</v>
       </c>
       <c r="M3" s="47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N3" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="O3" s="47">
         <v>255</v>
@@ -5895,7 +6258,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -5915,13 +6278,13 @@
         <v>122</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>122</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>1</v>
@@ -5933,10 +6296,10 @@
         <v>140</v>
       </c>
       <c r="M4" s="47" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O4" s="47">
         <v>255</v>
@@ -5967,7 +6330,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="31">
         <v>5</v>
       </c>
@@ -5993,7 +6356,7 @@
         <v>122</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J5" s="57" t="s">
         <v>1</v>
@@ -6005,10 +6368,10 @@
         <v>140</v>
       </c>
       <c r="M5" s="47" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N5" s="45" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="O5" s="47">
         <v>255</v>
@@ -6039,7 +6402,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -6059,7 +6422,7 @@
         <v>122</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H6" s="57" t="s">
         <v>1</v>
@@ -6077,22 +6440,22 @@
         <v>140</v>
       </c>
       <c r="M6" s="47" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N6" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O6" s="47">
         <v>255</v>
       </c>
       <c r="P6" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q6" s="47">
         <v>0</v>
       </c>
       <c r="R6" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S6" s="47">
         <v>0</v>
@@ -6104,14 +6467,14 @@
         <v>1</v>
       </c>
       <c r="V6" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W6" s="47" t="str">
         <f t="shared" ref="W6:W10" si="1">IF(OR(V6="cor.rgb",V6="cor.cmy",V6="cor.rgba",V6="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O6,".",Q6,".",S6,".",U6,""""), ".null",""), V6)</f>
         <v>"255.0.0"</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -6131,7 +6494,7 @@
         <v>122</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H7" s="57" t="s">
         <v>1</v>
@@ -6149,22 +6512,22 @@
         <v>140</v>
       </c>
       <c r="M7" s="47" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N7" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O7" s="47">
         <v>0</v>
       </c>
       <c r="P7" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q7" s="47">
         <v>255</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S7" s="47">
         <v>0</v>
@@ -6176,14 +6539,14 @@
         <v>1</v>
       </c>
       <c r="V7" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W7" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"0.255.0"</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -6203,7 +6566,7 @@
         <v>122</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H8" s="57" t="s">
         <v>1</v>
@@ -6221,22 +6584,22 @@
         <v>140</v>
       </c>
       <c r="M8" s="47" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N8" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O8" s="47">
         <v>0</v>
       </c>
       <c r="P8" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q8" s="47">
         <v>0</v>
       </c>
       <c r="R8" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S8" s="47">
         <v>255</v>
@@ -6248,14 +6611,14 @@
         <v>1</v>
       </c>
       <c r="V8" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W8" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"0.0.255"</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -6275,7 +6638,7 @@
         <v>122</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H9" s="57" t="s">
         <v>1</v>
@@ -6293,22 +6656,22 @@
         <v>140</v>
       </c>
       <c r="M9" s="47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N9" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O9" s="47">
         <v>200</v>
       </c>
       <c r="P9" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q9" s="47">
         <v>200</v>
       </c>
       <c r="R9" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S9" s="47">
         <v>200</v>
@@ -6320,14 +6683,14 @@
         <v>1</v>
       </c>
       <c r="V9" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W9" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"200.200.200"</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -6347,7 +6710,7 @@
         <v>122</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H10" s="57" t="s">
         <v>1</v>
@@ -6365,22 +6728,22 @@
         <v>140</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N10" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O10" s="47">
         <v>120</v>
       </c>
       <c r="P10" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q10" s="47">
         <v>120</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S10" s="47">
         <v>120</v>
@@ -6392,14 +6755,14 @@
         <v>1</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W10" s="47" t="str">
         <f t="shared" si="1"/>
         <v>"120.120.120"</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -6419,7 +6782,7 @@
         <v>122</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H11" s="57" t="s">
         <v>1</v>
@@ -6437,22 +6800,22 @@
         <v>140</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O11" s="47">
         <v>20</v>
       </c>
       <c r="P11" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q11" s="47">
         <v>20</v>
       </c>
       <c r="R11" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S11" s="47">
         <v>20</v>
@@ -6464,14 +6827,14 @@
         <v>1</v>
       </c>
       <c r="V11" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W11" s="47" t="str">
         <f>IF(OR(V11="cor.rgb",V11="cor.cmy",V11="cor.rgba",V11="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O11,".",Q11,".",S11,".",U11,""""), ".null",""), V11)</f>
         <v>"20.20.20"</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -6491,7 +6854,7 @@
         <v>122</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H12" s="57" t="s">
         <v>1</v>
@@ -6509,22 +6872,22 @@
         <v>140</v>
       </c>
       <c r="M12" s="47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N12" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O12" s="47">
         <v>150</v>
       </c>
       <c r="P12" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q12" s="47">
         <v>30</v>
       </c>
       <c r="R12" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S12" s="47">
         <v>10</v>
@@ -6536,14 +6899,14 @@
         <v>1</v>
       </c>
       <c r="V12" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W12" s="47" t="str">
         <f>IF(OR(V12="cor.rgb",V12="cor.cmy",V12="cor.rgba",V12="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O12,".",Q12,".",S12,".",U12,""""), ".null",""), V12)</f>
         <v>"150.30.10"</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -6563,7 +6926,7 @@
         <v>122</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H13" s="57" t="s">
         <v>1</v>
@@ -6581,22 +6944,22 @@
         <v>140</v>
       </c>
       <c r="M13" s="47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N13" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O13" s="47">
         <v>150</v>
       </c>
       <c r="P13" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Q13" s="47">
         <v>40</v>
       </c>
       <c r="R13" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S13" s="47">
         <v>10</v>
@@ -6608,14 +6971,14 @@
         <v>1</v>
       </c>
       <c r="V13" s="44" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W13" s="47" t="str">
         <f t="shared" ref="W13:W15" si="2">IF(OR(V13="cor.rgb",V13="cor.cmy",V13="cor.rgba",V13="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O13,".",Q13,".",S13,".",U13,""""), ".null",""), V13)</f>
         <v>"150.40.10"</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -6635,7 +6998,7 @@
         <v>122</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H14" s="57" t="s">
         <v>1</v>
@@ -6653,22 +7016,22 @@
         <v>140</v>
       </c>
       <c r="M14" s="47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N14" s="45" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O14" s="47">
         <v>150</v>
       </c>
       <c r="P14" s="45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q14" s="47">
         <v>50</v>
       </c>
       <c r="R14" s="44" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="S14" s="47">
         <v>10</v>
@@ -6680,14 +7043,14 @@
         <v>1</v>
       </c>
       <c r="V14" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="W14" s="47" t="str">
         <f t="shared" si="2"/>
         <v>"150.50.10"</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -6707,7 +7070,7 @@
         <v>122</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H15" s="57" t="s">
         <v>1</v>
@@ -6725,22 +7088,22 @@
         <v>140</v>
       </c>
       <c r="M15" s="47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N15" s="45" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O15" s="47">
         <v>150</v>
       </c>
       <c r="P15" s="45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q15" s="47">
         <v>60</v>
       </c>
       <c r="R15" s="44" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="S15" s="47">
         <v>10</v>
@@ -6752,14 +7115,14 @@
         <v>1</v>
       </c>
       <c r="V15" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="W15" s="47" t="str">
         <f t="shared" si="2"/>
         <v>"150.60.10"</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -6831,7 +7194,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -6869,7 +7232,7 @@
         <v>140</v>
       </c>
       <c r="M17" s="47" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N17" s="44" t="s">
         <v>133</v>
@@ -6903,12 +7266,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="31">
         <v>18</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>130</v>
@@ -6941,7 +7304,7 @@
         <v>140</v>
       </c>
       <c r="M18" s="47" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N18" s="52" t="s">
         <v>1</v>
@@ -6975,12 +7338,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="31">
         <v>19</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>128</v>
@@ -7013,7 +7376,7 @@
         <v>140</v>
       </c>
       <c r="M19" s="47" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N19" s="52" t="s">
         <v>1</v>
@@ -7047,12 +7410,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31">
         <v>20</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>129</v>
@@ -7085,7 +7448,7 @@
         <v>140</v>
       </c>
       <c r="M20" s="47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N20" s="52" t="s">
         <v>1</v>
@@ -7119,12 +7482,12 @@
         <v>null</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="31">
         <v>21</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>127</v>
@@ -7157,7 +7520,7 @@
         <v>140</v>
       </c>
       <c r="M21" s="47" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N21" s="52" t="s">
         <v>1</v>
@@ -7191,7 +7554,7 @@
         <v>null</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" s="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -7229,22 +7592,22 @@
         <v>140</v>
       </c>
       <c r="M22" s="47" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N22" s="45" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O22" s="47">
         <v>0</v>
       </c>
       <c r="P22" s="45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q22" s="47">
         <v>0</v>
       </c>
       <c r="R22" s="44" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="S22" s="47">
         <v>100</v>
@@ -7256,14 +7619,14 @@
         <v>1</v>
       </c>
       <c r="V22" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="W22" s="47" t="str">
         <f t="shared" ref="W22:W24" si="3">IF(OR(V22="cor.rgb",V22="cor.cmy",V22="cor.rgba",V22="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O22,".",Q22,".",S22,".",U22,""""), ".null",""), V22)</f>
         <v>"0.0.100"</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -7301,22 +7664,22 @@
         <v>140</v>
       </c>
       <c r="M23" s="47" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N23" s="45" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O23" s="47">
         <v>63</v>
       </c>
       <c r="P23" s="45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q23" s="47">
         <v>23</v>
       </c>
       <c r="R23" s="44" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="S23" s="47">
         <v>100</v>
@@ -7328,14 +7691,14 @@
         <v>1</v>
       </c>
       <c r="V23" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="W23" s="47" t="str">
         <f t="shared" si="3"/>
         <v>"63.23.100"</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -7373,22 +7736,22 @@
         <v>140</v>
       </c>
       <c r="M24" s="47" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N24" s="45" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O24" s="47">
         <v>100</v>
       </c>
       <c r="P24" s="45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q24" s="47">
         <v>0</v>
       </c>
       <c r="R24" s="44" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="S24" s="47">
         <v>100</v>
@@ -7400,14 +7763,14 @@
         <v>1</v>
       </c>
       <c r="V24" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="W24" s="47" t="str">
         <f t="shared" si="3"/>
         <v>"100.0.100"</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -7478,7 +7841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -7516,7 +7879,7 @@
         <v>140</v>
       </c>
       <c r="M26" s="47" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N26" s="52" t="s">
         <v>1</v>
@@ -7549,7 +7912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -7587,7 +7950,7 @@
         <v>140</v>
       </c>
       <c r="M27" s="47" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N27" s="52" t="s">
         <v>1</v>
@@ -7620,7 +7983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -7658,7 +8021,7 @@
         <v>140</v>
       </c>
       <c r="M28" s="47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N28" s="52" t="s">
         <v>1</v>
@@ -7691,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -7729,7 +8092,7 @@
         <v>140</v>
       </c>
       <c r="M29" s="47" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N29" s="52" t="s">
         <v>1</v>
@@ -7762,7 +8125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -7800,7 +8163,7 @@
         <v>140</v>
       </c>
       <c r="M30" s="47" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N30" s="52" t="s">
         <v>1</v>
@@ -7833,7 +8196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -7871,7 +8234,7 @@
         <v>140</v>
       </c>
       <c r="M31" s="47" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N31" s="52" t="s">
         <v>1</v>
@@ -7904,7 +8267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -7942,7 +8305,7 @@
         <v>140</v>
       </c>
       <c r="M32" s="47" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N32" s="52" t="s">
         <v>1</v>
@@ -7975,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -8013,7 +8376,7 @@
         <v>140</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N33" s="52" t="s">
         <v>1</v>
@@ -8046,7 +8409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -8084,7 +8447,7 @@
         <v>140</v>
       </c>
       <c r="M34" s="47" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N34" s="52" t="s">
         <v>1</v>
@@ -8117,7 +8480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -8155,7 +8518,7 @@
         <v>140</v>
       </c>
       <c r="M35" s="47" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N35" s="52" t="s">
         <v>1</v>
@@ -8188,7 +8551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -8259,7 +8622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -8297,7 +8660,7 @@
         <v>140</v>
       </c>
       <c r="M37" s="47" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N37" s="52" t="s">
         <v>1</v>
@@ -8330,7 +8693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -8368,7 +8731,7 @@
         <v>140</v>
       </c>
       <c r="M38" s="47" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N38" s="52" t="s">
         <v>1</v>
@@ -8401,7 +8764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -8439,7 +8802,7 @@
         <v>140</v>
       </c>
       <c r="M39" s="47" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N39" s="52" t="s">
         <v>1</v>
@@ -8472,7 +8835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="31">
         <v>40</v>
       </c>
@@ -8510,7 +8873,7 @@
         <v>140</v>
       </c>
       <c r="M40" s="47" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N40" s="52" t="s">
         <v>1</v>
@@ -8543,7 +8906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="31">
         <v>41</v>
       </c>
@@ -8581,7 +8944,7 @@
         <v>140</v>
       </c>
       <c r="M41" s="47" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N41" s="52" t="s">
         <v>1</v>
@@ -8614,7 +8977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="31">
         <v>42</v>
       </c>
@@ -8652,7 +9015,7 @@
         <v>140</v>
       </c>
       <c r="M42" s="47" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N42" s="52" t="s">
         <v>1</v>
@@ -8685,7 +9048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="31">
         <v>43</v>
       </c>
@@ -8723,7 +9086,7 @@
         <v>140</v>
       </c>
       <c r="M43" s="47" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N43" s="52" t="s">
         <v>1</v>
@@ -8756,7 +9119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="31">
         <v>44</v>
       </c>
@@ -8794,7 +9157,7 @@
         <v>140</v>
       </c>
       <c r="M44" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N44" s="52" t="s">
         <v>1</v>
@@ -8827,7 +9190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="31">
         <v>45</v>
       </c>
@@ -8865,7 +9228,7 @@
         <v>140</v>
       </c>
       <c r="M45" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N45" s="52" t="s">
         <v>1</v>
@@ -8898,7 +9261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="31">
         <v>46</v>
       </c>
@@ -8936,7 +9299,7 @@
         <v>140</v>
       </c>
       <c r="M46" s="47" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N46" s="52" t="s">
         <v>1</v>
@@ -8969,7 +9332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="31">
         <v>47</v>
       </c>
@@ -9007,7 +9370,7 @@
         <v>140</v>
       </c>
       <c r="M47" s="47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N47" s="52" t="s">
         <v>1</v>
@@ -9040,7 +9403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="31">
         <v>48</v>
       </c>
@@ -9078,7 +9441,7 @@
         <v>140</v>
       </c>
       <c r="M48" s="47" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N48" s="52" t="s">
         <v>1</v>
@@ -9111,7 +9474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="31">
         <v>49</v>
       </c>
@@ -9149,7 +9512,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="47" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N49" s="52" t="s">
         <v>1</v>
@@ -9182,7 +9545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -9220,7 +9583,7 @@
         <v>140</v>
       </c>
       <c r="M50" s="47" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N50" s="52" t="s">
         <v>1</v>
@@ -9253,7 +9616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -9291,7 +9654,7 @@
         <v>140</v>
       </c>
       <c r="M51" s="47" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N51" s="52" t="s">
         <v>1</v>
@@ -9324,7 +9687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -9362,7 +9725,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="55" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N52" s="54" t="s">
         <v>182</v>
@@ -9395,7 +9758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -9433,7 +9796,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="55" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N53" s="54" t="s">
         <v>182</v>
@@ -9466,7 +9829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -9504,7 +9867,7 @@
         <v>140</v>
       </c>
       <c r="M54" s="55" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N54" s="54" t="s">
         <v>182</v>
@@ -9537,7 +9900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -9608,7 +9971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -9679,7 +10042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -9750,7 +10113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -9821,7 +10184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -9892,7 +10255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -9963,7 +10326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -10034,7 +10397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -10141,15 +10504,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.3046875" customWidth="1"/>
+    <col min="4" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -10160,7 +10523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -10171,7 +10534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -10182,7 +10545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -10193,7 +10556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -10204,7 +10567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -10215,7 +10578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -10223,10 +10586,10 @@
         <v>28</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -10234,10 +10597,10 @@
         <v>37</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -10245,10 +10608,10 @@
         <v>36</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -10256,10 +10619,10 @@
         <v>35</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -10267,10 +10630,10 @@
         <v>34</v>
       </c>
       <c r="C11" s="69" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -10278,10 +10641,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="69" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -10289,10 +10652,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="69" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -10300,10 +10663,10 @@
         <v>31</v>
       </c>
       <c r="C14" s="69" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -10311,50 +10674,50 @@
         <v>30</v>
       </c>
       <c r="C15" s="29" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.75" x14ac:dyDescent="0.2">
+      <c r="C16" s="29" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+      <c r="C17" s="29" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
-      <c r="C16" s="29" t="s">
+    <row r="18" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+      <c r="C18" s="29" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
-      <c r="C17" s="29" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
-      <c r="C18" s="29" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C19" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C20" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C21" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C22" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C23" s="68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C24" s="68" t="s">
         <v>1</v>
       </c>

--- a/Versão5/PRO/Ontologia_Cromatica.xlsx
+++ b/Versão5/PRO/Ontologia_Cromatica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4CDD5F-FDFF-496F-90D0-6038FBB21DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ECBAB3-4626-4D34-8E65-8AFA93788130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -3215,55 +3215,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <b val="0"/>
@@ -3342,30 +3294,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3399,6 +3327,14 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -3409,24 +3345,6 @@
         <strike val="0"/>
         <color theme="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3451,6 +3369,24 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3813,15 +3749,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="58" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="58" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3832,7 +3768,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3843,7 +3779,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3854,7 +3790,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3865,7 +3801,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3877,7 +3813,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3889,7 +3825,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3900,7 +3836,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3911,7 +3847,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3922,7 +3858,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3933,7 +3869,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3944,7 +3880,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3955,7 +3891,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3966,7 +3902,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3977,7 +3913,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3988,7 +3924,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3999,7 +3935,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -4010,19 +3946,19 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46259.718232754632</v>
+        <v>46264.569491087961</v>
       </c>
       <c r="C18" s="57" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="40" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>256</v>
       </c>
@@ -4033,7 +3969,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="40" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>254</v>
       </c>
@@ -4045,7 +3981,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="40" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>255</v>
       </c>
@@ -4057,7 +3993,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -4068,7 +4004,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -4079,7 +4015,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -4090,7 +4026,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -4101,7 +4037,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>248</v>
       </c>
@@ -4121,37 +4057,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AC21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.53515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.69140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="108.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="113.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="108.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="66" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="108.15234375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="113.3828125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="108.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="66" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7" style="66" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.85546875" style="66" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.7109375" style="66" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" style="66" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="66" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.84375" style="66" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.69140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.69140625" style="66" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="6" style="66" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.28515625" style="66" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="66" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="66" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.3046875" style="66" customWidth="1"/>
+    <col min="27" max="27" width="4.84375" style="66" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="66" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.15234375" style="66" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
@@ -4240,7 +4176,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -4337,7 +4273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -4434,7 +4370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -4531,7 +4467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -4628,7 +4564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -4725,7 +4661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -4822,7 +4758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -4919,7 +4855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -5016,7 +4952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -5113,7 +5049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -5210,7 +5146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -5307,7 +5243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -5404,7 +5340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -5501,7 +5437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -5598,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -5695,7 +5631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -5792,7 +5728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -5889,7 +5825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -5986,7 +5922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -6083,7 +6019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -6094,10 +6030,10 @@
         <v>393</v>
       </c>
       <c r="D21" s="76" t="s">
+        <v>395</v>
+      </c>
+      <c r="E21" s="76" t="s">
         <v>394</v>
-      </c>
-      <c r="E21" s="76" t="s">
-        <v>395</v>
       </c>
       <c r="F21" s="76" t="s">
         <v>396</v>
@@ -6123,11 +6059,11 @@
       </c>
       <c r="M21" s="61" t="str">
         <f t="shared" si="7"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N21" s="61" t="str">
         <f t="shared" si="7"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O21" s="61" t="str">
         <f t="shared" si="7"/>
@@ -6151,11 +6087,11 @@
       </c>
       <c r="U21" s="56" t="str">
         <f t="shared" si="8"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V21" s="77" t="str">
         <f t="shared" si="8"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W21" s="56" t="s">
         <v>90</v>
@@ -6182,47 +6118,47 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B2 W20 B3:B20 A3:A21">
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B21">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:J1 C2:F19 T1:AC1 L2:Q19 T2:W19">
-    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20">
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F19 F22:F1048576">
-    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q1 K2:K13">
-    <cfRule type="cellIs" dxfId="27" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R19">
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+  <conditionalFormatting sqref="R21">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R21">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+  <conditionalFormatting sqref="W20">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6237,15 +6173,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="38" t="s">
         <v>22</v>
       </c>
@@ -6310,7 +6246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="38">
         <v>2</v>
       </c>
@@ -6378,7 +6314,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6390,14 +6326,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="35">
         <v>1</v>
       </c>
@@ -6408,7 +6344,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -6421,7 +6357,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6432,57 +6368,57 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:AU67"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" style="66" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" style="66" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="91.42578125" style="45" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.15234375" style="66" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.69140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.3046875" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="91.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.3828125" style="45" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.69140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.15234375" style="41" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.15234375" style="41" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.84375" style="41" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5" style="41" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.15234375" style="41" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="4" style="41" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="48" t="s">
         <v>91</v>
       </c>
@@ -6625,7 +6561,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="82">
         <v>2</v>
       </c>
@@ -6769,7 +6705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="82">
         <v>3</v>
       </c>
@@ -6913,7 +6849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="82">
         <v>4</v>
       </c>
@@ -7057,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="82">
         <v>5</v>
       </c>
@@ -7201,7 +7137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="82">
         <v>6</v>
       </c>
@@ -7275,7 +7211,7 @@
         <v>340</v>
       </c>
       <c r="Y6" s="46" t="str">
-        <f>IF(OR(X6="cor.rgb",X6="cor.cmy",X6="cor.rgba",X6="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q6,".",S6,".",U6,".",W6,""""), ".null",""), X6)</f>
+        <f t="shared" ref="Y6:Y15" si="0">IF(OR(X6="cor.rgb",X6="cor.cmy",X6="cor.rgba",X6="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q6,".",S6,".",U6,".",W6,""""), ".null",""), X6)</f>
         <v>"255.0.0"</v>
       </c>
       <c r="Z6" s="43" t="s">
@@ -7345,7 +7281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="82">
         <v>7</v>
       </c>
@@ -7419,7 +7355,7 @@
         <v>340</v>
       </c>
       <c r="Y7" s="46" t="str">
-        <f>IF(OR(X7="cor.rgb",X7="cor.cmy",X7="cor.rgba",X7="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q7,".",S7,".",U7,".",W7,""""), ".null",""), X7)</f>
+        <f t="shared" si="0"/>
         <v>"0.255.0"</v>
       </c>
       <c r="Z7" s="43" t="s">
@@ -7489,7 +7425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="82">
         <v>8</v>
       </c>
@@ -7563,7 +7499,7 @@
         <v>340</v>
       </c>
       <c r="Y8" s="46" t="str">
-        <f>IF(OR(X8="cor.rgb",X8="cor.cmy",X8="cor.rgba",X8="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q8,".",S8,".",U8,".",W8,""""), ".null",""), X8)</f>
+        <f t="shared" si="0"/>
         <v>"0.0.255"</v>
       </c>
       <c r="Z8" s="43" t="s">
@@ -7633,7 +7569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="82">
         <v>9</v>
       </c>
@@ -7707,7 +7643,7 @@
         <v>340</v>
       </c>
       <c r="Y9" s="46" t="str">
-        <f>IF(OR(X9="cor.rgb",X9="cor.cmy",X9="cor.rgba",X9="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q9,".",S9,".",U9,".",W9,""""), ".null",""), X9)</f>
+        <f t="shared" si="0"/>
         <v>"200.200.200"</v>
       </c>
       <c r="Z9" s="43" t="s">
@@ -7777,7 +7713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="82">
         <v>10</v>
       </c>
@@ -7851,7 +7787,7 @@
         <v>340</v>
       </c>
       <c r="Y10" s="46" t="str">
-        <f>IF(OR(X10="cor.rgb",X10="cor.cmy",X10="cor.rgba",X10="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q10,".",S10,".",U10,".",W10,""""), ".null",""), X10)</f>
+        <f t="shared" si="0"/>
         <v>"120.120.120"</v>
       </c>
       <c r="Z10" s="43" t="s">
@@ -7921,7 +7857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="82">
         <v>11</v>
       </c>
@@ -7995,7 +7931,7 @@
         <v>340</v>
       </c>
       <c r="Y11" s="46" t="str">
-        <f>IF(OR(X11="cor.rgb",X11="cor.cmy",X11="cor.rgba",X11="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q11,".",S11,".",U11,".",W11,""""), ".null",""), X11)</f>
+        <f t="shared" si="0"/>
         <v>"20.20.20"</v>
       </c>
       <c r="Z11" s="43" t="s">
@@ -8065,7 +8001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="82">
         <v>12</v>
       </c>
@@ -8139,7 +8075,7 @@
         <v>340</v>
       </c>
       <c r="Y12" s="46" t="str">
-        <f>IF(OR(X12="cor.rgb",X12="cor.cmy",X12="cor.rgba",X12="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q12,".",S12,".",U12,".",W12,""""), ".null",""), X12)</f>
+        <f t="shared" si="0"/>
         <v>"150.30.10"</v>
       </c>
       <c r="Z12" s="43" t="s">
@@ -8209,7 +8145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="82">
         <v>13</v>
       </c>
@@ -8283,7 +8219,7 @@
         <v>340</v>
       </c>
       <c r="Y13" s="46" t="str">
-        <f>IF(OR(X13="cor.rgb",X13="cor.cmy",X13="cor.rgba",X13="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q13,".",S13,".",U13,".",W13,""""), ".null",""), X13)</f>
+        <f t="shared" si="0"/>
         <v>"150.40.10"</v>
       </c>
       <c r="Z13" s="43" t="s">
@@ -8353,7 +8289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="82">
         <v>14</v>
       </c>
@@ -8427,7 +8363,7 @@
         <v>341</v>
       </c>
       <c r="Y14" s="46" t="str">
-        <f>IF(OR(X14="cor.rgb",X14="cor.cmy",X14="cor.rgba",X14="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q14,".",S14,".",U14,".",W14,""""), ".null",""), X14)</f>
+        <f t="shared" si="0"/>
         <v>"150.50.10"</v>
       </c>
       <c r="Z14" s="43" t="s">
@@ -8497,7 +8433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="82">
         <v>15</v>
       </c>
@@ -8571,7 +8507,7 @@
         <v>341</v>
       </c>
       <c r="Y15" s="46" t="str">
-        <f>IF(OR(X15="cor.rgb",X15="cor.cmy",X15="cor.rgba",X15="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q15,".",S15,".",U15,".",W15,""""), ".null",""), X15)</f>
+        <f t="shared" si="0"/>
         <v>"150.60.10"</v>
       </c>
       <c r="Z15" s="43" t="s">
@@ -8641,7 +8577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="82">
         <v>16</v>
       </c>
@@ -8715,7 +8651,7 @@
         <v>1</v>
       </c>
       <c r="Y16" s="46" t="str">
-        <f>IF(OR(X16="rgb",X16="cmy",X16="rgba",X16="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q16,".",S16,".",U16,".",W16,""""), ".null",""), X16)</f>
+        <f t="shared" ref="Y16:Y21" si="1">IF(OR(X16="rgb",X16="cmy",X16="rgba",X16="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q16,".",S16,".",U16,".",W16,""""), ".null",""), X16)</f>
         <v>null</v>
       </c>
       <c r="Z16" s="43" t="s">
@@ -8785,7 +8721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="82">
         <v>17</v>
       </c>
@@ -8859,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="Y17" s="46" t="str">
-        <f>IF(OR(X17="rgb",X17="cmy",X17="rgba",X17="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q17,".",S17,".",U17,".",W17,""""), ".null",""), X17)</f>
+        <f t="shared" si="1"/>
         <v>null</v>
       </c>
       <c r="Z17" s="43" t="s">
@@ -8929,7 +8865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="82">
         <v>18</v>
       </c>
@@ -9003,7 +8939,7 @@
         <v>1</v>
       </c>
       <c r="Y18" s="46" t="str">
-        <f>IF(OR(X18="rgb",X18="cmy",X18="rgba",X18="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q18,".",S18,".",U18,".",W18,""""), ".null",""), X18)</f>
+        <f t="shared" si="1"/>
         <v>null</v>
       </c>
       <c r="Z18" s="43" t="s">
@@ -9073,7 +9009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="82">
         <v>19</v>
       </c>
@@ -9147,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="Y19" s="46" t="str">
-        <f>IF(OR(X19="rgb",X19="cmy",X19="rgba",X19="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q19,".",S19,".",U19,".",W19,""""), ".null",""), X19)</f>
+        <f t="shared" si="1"/>
         <v>null</v>
       </c>
       <c r="Z19" s="43" t="s">
@@ -9217,7 +9153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="82">
         <v>20</v>
       </c>
@@ -9291,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="Y20" s="46" t="str">
-        <f>IF(OR(X20="rgb",X20="cmy",X20="rgba",X20="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q20,".",S20,".",U20,".",W20,""""), ".null",""), X20)</f>
+        <f t="shared" si="1"/>
         <v>null</v>
       </c>
       <c r="Z20" s="43" t="s">
@@ -9361,7 +9297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="82">
         <v>21</v>
       </c>
@@ -9435,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="Y21" s="46" t="str">
-        <f>IF(OR(X21="rgb",X21="cmy",X21="rgba",X21="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q21,".",S21,".",U21,".",W21,""""), ".null",""), X21)</f>
+        <f t="shared" si="1"/>
         <v>null</v>
       </c>
       <c r="Z21" s="43" t="s">
@@ -9505,7 +9441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="82">
         <v>22</v>
       </c>
@@ -9649,7 +9585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="82">
         <v>23</v>
       </c>
@@ -9793,7 +9729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="82">
         <v>24</v>
       </c>
@@ -9937,7 +9873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="82">
         <v>25</v>
       </c>
@@ -10080,7 +10016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="82">
         <v>26</v>
       </c>
@@ -10223,7 +10159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="82">
         <v>27</v>
       </c>
@@ -10366,7 +10302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="82">
         <v>28</v>
       </c>
@@ -10509,7 +10445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="82">
         <v>29</v>
       </c>
@@ -10652,7 +10588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="82">
         <v>30</v>
       </c>
@@ -10795,7 +10731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="82">
         <v>31</v>
       </c>
@@ -10938,7 +10874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="82">
         <v>32</v>
       </c>
@@ -11081,7 +11017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="82">
         <v>33</v>
       </c>
@@ -11224,7 +11160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="82">
         <v>34</v>
       </c>
@@ -11367,7 +11303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="82">
         <v>35</v>
       </c>
@@ -11510,7 +11446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="82">
         <v>36</v>
       </c>
@@ -11653,7 +11589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="82">
         <v>37</v>
       </c>
@@ -11796,7 +11732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="82">
         <v>38</v>
       </c>
@@ -11939,7 +11875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="82">
         <v>39</v>
       </c>
@@ -12082,7 +12018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="82">
         <v>40</v>
       </c>
@@ -12225,7 +12161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="82">
         <v>41</v>
       </c>
@@ -12368,7 +12304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="82">
         <v>42</v>
       </c>
@@ -12511,7 +12447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="82">
         <v>43</v>
       </c>
@@ -12654,7 +12590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="82">
         <v>44</v>
       </c>
@@ -12797,7 +12733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="82">
         <v>45</v>
       </c>
@@ -12940,7 +12876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="82">
         <v>46</v>
       </c>
@@ -13083,7 +13019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="82">
         <v>47</v>
       </c>
@@ -13226,7 +13162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="82">
         <v>48</v>
       </c>
@@ -13369,7 +13305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="82">
         <v>49</v>
       </c>
@@ -13512,7 +13448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="82">
         <v>50</v>
       </c>
@@ -13655,7 +13591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="82">
         <v>51</v>
       </c>
@@ -13798,7 +13734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="82">
         <v>52</v>
       </c>
@@ -13941,7 +13877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="82">
         <v>53</v>
       </c>
@@ -14084,7 +14020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="82">
         <v>54</v>
       </c>
@@ -14227,7 +14163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="82">
         <v>55</v>
       </c>
@@ -14370,7 +14306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="82">
         <v>56</v>
       </c>
@@ -14513,7 +14449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="82">
         <v>57</v>
       </c>
@@ -14656,7 +14592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="82">
         <v>58</v>
       </c>
@@ -14799,7 +14735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="82">
         <v>59</v>
       </c>
@@ -14942,7 +14878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="82">
         <v>60</v>
       </c>
@@ -15085,7 +15021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="82">
         <v>61</v>
       </c>
@@ -15228,7 +15164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="82">
         <v>62</v>
       </c>
@@ -15371,7 +15307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="82">
         <v>63</v>
       </c>
@@ -15478,7 +15414,7 @@
         <v>405</v>
       </c>
       <c r="AJ63" s="88" t="str">
-        <f t="shared" ref="AJ63:AJ67" si="0">IF(AK63="null", "null", "método.revit")</f>
+        <f t="shared" ref="AJ63:AJ67" si="2">IF(AK63="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="AK63" s="89" t="s">
@@ -15515,7 +15451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="82">
         <v>64</v>
       </c>
@@ -15622,7 +15558,7 @@
         <v>409</v>
       </c>
       <c r="AJ64" s="88" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK64" s="89" t="s">
@@ -15659,7 +15595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="82">
         <v>65</v>
       </c>
@@ -15766,7 +15702,7 @@
         <v>413</v>
       </c>
       <c r="AJ65" s="88" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK65" s="89" t="s">
@@ -15803,7 +15739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="82">
         <v>66</v>
       </c>
@@ -15910,7 +15846,7 @@
         <v>417</v>
       </c>
       <c r="AJ66" s="88" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK66" s="89" t="s">
@@ -15947,7 +15883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="82">
         <v>67</v>
       </c>
@@ -16054,7 +15990,7 @@
         <v>421</v>
       </c>
       <c r="AJ67" s="88" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK67" s="89" t="s">
@@ -16096,76 +16032,51 @@
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B18 B20:B21 R16:S18 N22:Y31 L18:M62 AV19:XFD19 AV22:XFD62 AV1:XFD17 L16:O17 B19:I19 A1:I2 J1:K62 N19:AA19 Z22:AA62 Z1:AA17 L1:Y15 T16:Y17 L32:Y62 B22:I62 B3:I17 A68:AS1048576 H63:I67 X63:AC67 P63:Q67 AB1:AS62 AL63:AS67 AV68:XFD1048576 AT1:AU1048576 A3:A67">
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
+  <conditionalFormatting sqref="A1:I2 B3:I17 B18 B19:I19 B20:B21 B22:I62 A68:AS1048576 L1:Y15 Z1:AA17 AB1:AS62 AT1:AU1048576 A3:A67 T16:Y17 R16:S18 N22:Y31 Z22:AA62 L32:Y62 AL63:AS67 AV68:XFD1048576">
+    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B62 B68:B1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:B67">
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:Q18 P16:Q17 AV18:XFD18 C18:I18 T18:AA18">
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+  <conditionalFormatting sqref="C18:I18 AV1:XFD62 L16:Q17 N18:Q18 T18:AA18">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV20:XFD21 C20:I21 N20:AA21">
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+  <conditionalFormatting sqref="C20:I21 N19:AA21">
+    <cfRule type="cellIs" dxfId="5" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B67">
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D63:E67">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+  <conditionalFormatting sqref="D63:I67">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F63:G67">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+  <conditionalFormatting sqref="J1:K67">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R63:W67">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+  <conditionalFormatting sqref="L18:M67">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD63:AE67">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L63:M67">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J63:K63">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J64:K64">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J65:K65">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J66:K67">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="P63:AE67">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16176,15 +16087,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.3046875" customWidth="1"/>
+    <col min="4" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -16195,7 +16106,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -16206,7 +16117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -16217,7 +16128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -16228,7 +16139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -16239,7 +16150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -16250,7 +16161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -16261,7 +16172,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -16272,7 +16183,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -16283,7 +16194,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -16294,7 +16205,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -16305,7 +16216,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -16316,7 +16227,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -16327,7 +16238,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -16338,7 +16249,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -16349,54 +16260,54 @@
         <v>307</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C16" s="29" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C17" s="29" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C18" s="29" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C19" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C20" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C21" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C22" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C23" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
       <c r="C24" s="64" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1 C7:C18">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Cromatica.xlsx
+++ b/Versão5/PRO/Ontologia_Cromatica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ECBAB3-4626-4D34-8E65-8AFA93788130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3E9F92-3930-46D3-BABC-D0E39BBBBD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3702" uniqueCount="441">
   <si>
     <t>Key</t>
   </si>
@@ -2452,18 +2452,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2531,6 +2519,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2837,12 +2891,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
@@ -2875,6 +2923,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3162,16 +3216,10 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3183,10 +3231,10 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3195,27 +3243,33 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -3364,19 +3418,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3749,15 +3797,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="58" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3768,7 +3816,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3779,7 +3827,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3790,7 +3838,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3801,7 +3849,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3813,7 +3861,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3825,7 +3873,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3836,7 +3884,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3847,7 +3895,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3858,7 +3906,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3869,7 +3917,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3880,7 +3928,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3891,7 +3939,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3902,7 +3950,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3913,7 +3961,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3924,7 +3972,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3935,7 +3983,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3946,19 +3994,19 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46264.569491087961</v>
+        <v>46268.698612615743</v>
       </c>
       <c r="C18" s="57" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="40" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>256</v>
       </c>
@@ -3969,7 +4017,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="40" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>254</v>
       </c>
@@ -3981,7 +4029,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="40" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>255</v>
       </c>
@@ -3993,7 +4041,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -4004,7 +4052,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -4015,7 +4063,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -4026,7 +4074,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -4037,7 +4085,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>248</v>
       </c>
@@ -4056,38 +4104,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AC21"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="108.15234375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="113.3828125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="108.3828125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="108.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="113.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="66" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7" style="66" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.84375" style="66" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.69140625" style="66" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.53515625" style="66" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.85546875" style="66" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" style="66" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="66" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="6" style="66" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.3046875" style="66" customWidth="1"/>
-    <col min="27" max="27" width="4.84375" style="66" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" style="66" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.15234375" style="66" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" style="66" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="66" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="66" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="3.28515625" style="66" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
@@ -4175,8 +4223,11 @@
       <c r="AC1" s="24" t="s">
         <v>246</v>
       </c>
+      <c r="AD1" s="24" t="s">
+        <v>440</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -4254,26 +4305,29 @@
         <v>90</v>
       </c>
       <c r="X2" s="73" t="str">
-        <f t="shared" ref="X2:X21" si="2">CONCATENATE("Key-CROMA-",A2)</f>
+        <f t="shared" ref="X2:X19" si="2">CONCATENATE("Key-CROMA-",A2)</f>
         <v>Key-CROMA-2</v>
       </c>
-      <c r="Y2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="78" t="s">
+      <c r="Y2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -4354,23 +4408,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-3</v>
       </c>
-      <c r="Y3" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="78" t="s">
+      <c r="Y3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -4451,23 +4508,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-4</v>
       </c>
-      <c r="Y4" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="78" t="s">
+      <c r="Y4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -4548,23 +4608,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-5</v>
       </c>
-      <c r="Y5" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="78" t="s">
+      <c r="Y5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -4645,23 +4708,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-6</v>
       </c>
-      <c r="Y6" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="78" t="s">
+      <c r="Y6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -4742,23 +4808,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-7</v>
       </c>
-      <c r="Y7" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="78" t="s">
+      <c r="Y7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -4839,23 +4908,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-8</v>
       </c>
-      <c r="Y8" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="78" t="s">
+      <c r="Y8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -4936,23 +5008,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-9</v>
       </c>
-      <c r="Y9" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="78" t="s">
+      <c r="Y9" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -5033,23 +5108,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-10</v>
       </c>
-      <c r="Y10" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="78" t="s">
+      <c r="Y10" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -5130,23 +5208,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-11</v>
       </c>
-      <c r="Y11" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="78" t="s">
+      <c r="Y11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -5227,23 +5308,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-12</v>
       </c>
-      <c r="Y12" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="78" t="s">
+      <c r="Y12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -5324,23 +5408,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-13</v>
       </c>
-      <c r="Y13" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="78" t="s">
+      <c r="Y13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -5421,23 +5508,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-14</v>
       </c>
-      <c r="Y14" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="78" t="s">
+      <c r="Y14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -5518,23 +5608,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-15</v>
       </c>
-      <c r="Y15" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="78" t="s">
+      <c r="Y15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -5615,23 +5708,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-16</v>
       </c>
-      <c r="Y16" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="78" t="s">
+      <c r="Y16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -5712,23 +5808,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-17</v>
       </c>
-      <c r="Y17" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="78" t="s">
+      <c r="Y17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -5809,23 +5908,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-18</v>
       </c>
-      <c r="Y18" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="78" t="s">
+      <c r="Y18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -5906,23 +6008,26 @@
         <f t="shared" si="2"/>
         <v>Key-CROMA-19</v>
       </c>
-      <c r="Y19" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="78" t="s">
+      <c r="Y19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -6000,43 +6105,46 @@
         <v>90</v>
       </c>
       <c r="X20" s="73" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="X20:X25" si="7">CONCATENATE("Key-CROMA-",A20)</f>
         <v>Key-CROMA-20</v>
       </c>
-      <c r="Y20" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="78" t="s">
+      <c r="Y20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="60">
         <v>21</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="90" t="s">
         <v>345</v>
       </c>
-      <c r="C21" s="76" t="s">
+      <c r="C21" s="91" t="s">
         <v>393</v>
       </c>
-      <c r="D21" s="76" t="s">
+      <c r="D21" s="91" t="s">
         <v>395</v>
       </c>
-      <c r="E21" s="76" t="s">
+      <c r="E21" s="91" t="s">
         <v>394</v>
       </c>
-      <c r="F21" s="76" t="s">
-        <v>396</v>
+      <c r="F21" s="91" t="s">
+        <v>419</v>
       </c>
       <c r="G21" s="64" t="s">
         <v>1</v>
@@ -6054,111 +6162,507 @@
         <v>1</v>
       </c>
       <c r="L21" s="61" t="str">
-        <f t="shared" ref="L21:O21" si="7">SUBSTITUTE(CONCATENATE("", C21), ".", " ")</f>
+        <f t="shared" ref="L21:O25" si="8">SUBSTITUTE(CONCATENATE("", C21), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M21" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>Macros</v>
-      </c>
-      <c r="N21" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O21" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P21" s="56" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q21" s="56" t="s">
-        <v>398</v>
-      </c>
-      <c r="R21" s="56" t="s">
-        <v>399</v>
-      </c>
-      <c r="S21" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="56" t="str">
-        <f t="shared" ref="T21:V21" si="8">SUBSTITUTE(C21, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U21" s="56" t="str">
         <f t="shared" si="8"/>
         <v>Macros</v>
       </c>
-      <c r="V21" s="77" t="str">
+      <c r="N21" s="61" t="str">
         <f t="shared" si="8"/>
         <v>Métodos</v>
       </c>
+      <c r="O21" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P21" s="56" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q21" s="56" t="s">
+        <v>421</v>
+      </c>
+      <c r="R21" s="56" t="s">
+        <v>422</v>
+      </c>
+      <c r="S21" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="56" t="str">
+        <f t="shared" ref="T21:V25" si="9">SUBSTITUTE(C21, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U21" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>Macros</v>
+      </c>
+      <c r="V21" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>Métodos</v>
+      </c>
       <c r="W21" s="56" t="s">
         <v>90</v>
       </c>
       <c r="X21" s="73" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Key-CROMA-21</v>
       </c>
-      <c r="Y21" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="78" t="s">
+      <c r="Y21" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="60">
+        <v>22</v>
+      </c>
+      <c r="B22" s="90" t="s">
+        <v>345</v>
+      </c>
+      <c r="C22" s="91" t="s">
+        <v>393</v>
+      </c>
+      <c r="D22" s="91" t="s">
+        <v>395</v>
+      </c>
+      <c r="E22" s="91" t="s">
+        <v>394</v>
+      </c>
+      <c r="F22" s="91" t="s">
+        <v>423</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>De API</v>
+      </c>
+      <c r="M22" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Macros</v>
+      </c>
+      <c r="N22" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O22" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P22" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q22" s="56" t="s">
+        <v>425</v>
+      </c>
+      <c r="R22" s="56" t="s">
+        <v>426</v>
+      </c>
+      <c r="S22" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>De API</v>
+      </c>
+      <c r="U22" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>Macros</v>
+      </c>
+      <c r="V22" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W22" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="X22" s="73" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-CROMA-22</v>
+      </c>
+      <c r="Y22" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="60">
+        <v>23</v>
+      </c>
+      <c r="B23" s="90" t="s">
+        <v>345</v>
+      </c>
+      <c r="C23" s="91" t="s">
+        <v>393</v>
+      </c>
+      <c r="D23" s="91" t="s">
+        <v>395</v>
+      </c>
+      <c r="E23" s="91" t="s">
+        <v>394</v>
+      </c>
+      <c r="F23" s="91" t="s">
+        <v>427</v>
+      </c>
+      <c r="G23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>De API</v>
+      </c>
+      <c r="M23" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Macros</v>
+      </c>
+      <c r="N23" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O23" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P23" s="56" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q23" s="56" t="s">
+        <v>429</v>
+      </c>
+      <c r="R23" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="S23" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>De API</v>
+      </c>
+      <c r="U23" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>Macros</v>
+      </c>
+      <c r="V23" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W23" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="X23" s="73" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-CROMA-23</v>
+      </c>
+      <c r="Y23" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="60">
+        <v>24</v>
+      </c>
+      <c r="B24" s="90" t="s">
+        <v>345</v>
+      </c>
+      <c r="C24" s="91" t="s">
+        <v>393</v>
+      </c>
+      <c r="D24" s="91" t="s">
+        <v>395</v>
+      </c>
+      <c r="E24" s="91" t="s">
+        <v>394</v>
+      </c>
+      <c r="F24" s="91" t="s">
+        <v>431</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>De API</v>
+      </c>
+      <c r="M24" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Macros</v>
+      </c>
+      <c r="N24" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O24" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P24" s="56" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q24" s="56" t="s">
+        <v>433</v>
+      </c>
+      <c r="R24" s="56" t="s">
+        <v>434</v>
+      </c>
+      <c r="S24" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>De API</v>
+      </c>
+      <c r="U24" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>Macros</v>
+      </c>
+      <c r="V24" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W24" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="X24" s="73" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-CROMA-24</v>
+      </c>
+      <c r="Y24" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="60">
+        <v>25</v>
+      </c>
+      <c r="B25" s="90" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" s="91" t="s">
+        <v>393</v>
+      </c>
+      <c r="D25" s="91" t="s">
+        <v>395</v>
+      </c>
+      <c r="E25" s="91" t="s">
+        <v>435</v>
+      </c>
+      <c r="F25" s="91" t="s">
+        <v>436</v>
+      </c>
+      <c r="G25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>De API</v>
+      </c>
+      <c r="M25" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Macros</v>
+      </c>
+      <c r="N25" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O25" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P25" s="56" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q25" s="56" t="s">
+        <v>438</v>
+      </c>
+      <c r="R25" s="56" t="s">
+        <v>439</v>
+      </c>
+      <c r="S25" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>De API</v>
+      </c>
+      <c r="U25" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>Macros</v>
+      </c>
+      <c r="V25" s="75" t="str">
+        <f t="shared" si="9"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W25" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="X25" s="73" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-CROMA-25</v>
+      </c>
+      <c r="Y25" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="76" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B21">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B25">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:J1 C2:F19 T1:AC1 L2:Q19 T2:W19">
-    <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
+  <conditionalFormatting sqref="A1:J1 C2:F19 T1:AD1 L2:Q19 T2:W19 W20:W25">
+    <cfRule type="cellIs" dxfId="22" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20">
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F19 F22:F1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+  <conditionalFormatting sqref="E25:F25">
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F19 F26:F1048576">
+    <cfRule type="duplicateValues" dxfId="19" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+  <conditionalFormatting sqref="F21:F24">
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q1 K2:K13">
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R19">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R21">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W20">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6173,15 +6677,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="38" t="s">
         <v>22</v>
       </c>
@@ -6246,7 +6750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="38">
         <v>2</v>
       </c>
@@ -6326,14 +6830,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="35">
         <v>1</v>
       </c>
@@ -6344,7 +6848,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -6368,57 +6872,57 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:AU67"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.15234375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.15234375" style="66" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69140625" style="66" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="91.3828125" style="45" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="66" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="91.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" style="45" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="46.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.69140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.84375" style="41" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.15234375" style="41" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.84375" style="41" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.15234375" style="41" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.84375" style="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.85546875" style="41" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5" style="41" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.15234375" style="41" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.3828125" style="41" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.84375" style="41" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="4" style="41" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.3046875" style="41" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:47" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
         <v>91</v>
       </c>
@@ -6561,8 +7065,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="82">
+    <row r="2" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="80">
         <v>2</v>
       </c>
       <c r="B2" s="33" t="s">
@@ -6592,13 +7096,13 @@
       <c r="J2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="80" t="s">
+      <c r="K2" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="80" t="s">
+      <c r="M2" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N2" s="43" t="s">
@@ -6705,8 +7209,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="82">
+    <row r="3" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="80">
         <v>3</v>
       </c>
       <c r="B3" s="33" t="s">
@@ -6736,13 +7240,13 @@
       <c r="J3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="80" t="s">
+      <c r="K3" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="80" t="s">
+      <c r="M3" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N3" s="43" t="s">
@@ -6849,8 +7353,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="82">
+    <row r="4" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="80">
         <v>4</v>
       </c>
       <c r="B4" s="33" t="s">
@@ -6880,13 +7384,13 @@
       <c r="J4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="80" t="s">
+      <c r="K4" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="80" t="s">
+      <c r="M4" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N4" s="43" t="s">
@@ -6993,8 +7497,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="82">
+    <row r="5" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="80">
         <v>5</v>
       </c>
       <c r="B5" s="33" t="s">
@@ -7024,13 +7528,13 @@
       <c r="J5" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="80" t="s">
+      <c r="K5" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="80" t="s">
+      <c r="M5" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N5" s="43" t="s">
@@ -7137,8 +7641,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="82">
+    <row r="6" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="80">
         <v>6</v>
       </c>
       <c r="B6" s="33" t="s">
@@ -7168,13 +7672,13 @@
       <c r="J6" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K6" s="80" t="s">
+      <c r="K6" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M6" s="80" t="s">
+      <c r="M6" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="43" t="s">
@@ -7281,8 +7785,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="82">
+    <row r="7" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="80">
         <v>7</v>
       </c>
       <c r="B7" s="33" t="s">
@@ -7312,13 +7816,13 @@
       <c r="J7" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="80" t="s">
+      <c r="K7" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M7" s="80" t="s">
+      <c r="M7" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N7" s="43" t="s">
@@ -7425,8 +7929,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="82">
+    <row r="8" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="80">
         <v>8</v>
       </c>
       <c r="B8" s="33" t="s">
@@ -7456,13 +7960,13 @@
       <c r="J8" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K8" s="80" t="s">
+      <c r="K8" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M8" s="80" t="s">
+      <c r="M8" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N8" s="43" t="s">
@@ -7569,8 +8073,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="82">
+    <row r="9" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="80">
         <v>9</v>
       </c>
       <c r="B9" s="33" t="s">
@@ -7600,13 +8104,13 @@
       <c r="J9" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="80" t="s">
+      <c r="K9" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M9" s="80" t="s">
+      <c r="M9" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N9" s="43" t="s">
@@ -7713,8 +8217,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="82">
+    <row r="10" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="80">
         <v>10</v>
       </c>
       <c r="B10" s="33" t="s">
@@ -7744,13 +8248,13 @@
       <c r="J10" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K10" s="80" t="s">
+      <c r="K10" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="80" t="s">
+      <c r="M10" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N10" s="43" t="s">
@@ -7857,8 +8361,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="82">
+    <row r="11" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="80">
         <v>11</v>
       </c>
       <c r="B11" s="33" t="s">
@@ -7888,13 +8392,13 @@
       <c r="J11" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K11" s="80" t="s">
+      <c r="K11" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L11" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M11" s="80" t="s">
+      <c r="M11" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N11" s="43" t="s">
@@ -8001,8 +8505,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="82">
+    <row r="12" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="80">
         <v>12</v>
       </c>
       <c r="B12" s="33" t="s">
@@ -8032,13 +8536,13 @@
       <c r="J12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K12" s="80" t="s">
+      <c r="K12" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M12" s="80" t="s">
+      <c r="M12" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N12" s="43" t="s">
@@ -8145,8 +8649,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="82">
+    <row r="13" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="80">
         <v>13</v>
       </c>
       <c r="B13" s="33" t="s">
@@ -8176,13 +8680,13 @@
       <c r="J13" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K13" s="80" t="s">
+      <c r="K13" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L13" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="80" t="s">
+      <c r="M13" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N13" s="43" t="s">
@@ -8289,8 +8793,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="82">
+    <row r="14" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="80">
         <v>14</v>
       </c>
       <c r="B14" s="33" t="s">
@@ -8320,13 +8824,13 @@
       <c r="J14" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K14" s="80" t="s">
+      <c r="K14" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L14" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="80" t="s">
+      <c r="M14" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N14" s="43" t="s">
@@ -8433,8 +8937,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="82">
+    <row r="15" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="80">
         <v>15</v>
       </c>
       <c r="B15" s="33" t="s">
@@ -8464,13 +8968,13 @@
       <c r="J15" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K15" s="80" t="s">
+      <c r="K15" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="80" t="s">
+      <c r="M15" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N15" s="43" t="s">
@@ -8577,8 +9081,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="82">
+    <row r="16" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="80">
         <v>16</v>
       </c>
       <c r="B16" s="33" t="s">
@@ -8608,7 +9112,7 @@
       <c r="J16" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K16" s="80" t="s">
+      <c r="K16" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L16" s="43" t="s">
@@ -8623,7 +9127,7 @@
       <c r="O16" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="P16" s="81" t="s">
+      <c r="P16" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q16" s="46" t="s">
@@ -8721,8 +9225,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="82">
+    <row r="17" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="80">
         <v>17</v>
       </c>
       <c r="B17" s="33" t="s">
@@ -8752,7 +9256,7 @@
       <c r="J17" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K17" s="80" t="s">
+      <c r="K17" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L17" s="43" t="s">
@@ -8767,7 +9271,7 @@
       <c r="O17" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="P17" s="81" t="s">
+      <c r="P17" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q17" s="46" t="s">
@@ -8865,8 +9369,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="82">
+    <row r="18" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="80">
         <v>18</v>
       </c>
       <c r="B18" s="33" t="s">
@@ -8896,13 +9400,13 @@
       <c r="J18" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K18" s="80" t="s">
+      <c r="K18" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L18" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M18" s="80" t="s">
+      <c r="M18" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N18" s="43" t="s">
@@ -8911,7 +9415,7 @@
       <c r="O18" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="P18" s="81" t="s">
+      <c r="P18" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q18" s="46" t="s">
@@ -9009,8 +9513,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="82">
+    <row r="19" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="80">
         <v>19</v>
       </c>
       <c r="B19" s="33" t="s">
@@ -9040,13 +9544,13 @@
       <c r="J19" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K19" s="80" t="s">
+      <c r="K19" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L19" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="80" t="s">
+      <c r="M19" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N19" s="43" t="s">
@@ -9055,7 +9559,7 @@
       <c r="O19" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="P19" s="81" t="s">
+      <c r="P19" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q19" s="46" t="s">
@@ -9153,8 +9657,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="82">
+    <row r="20" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="80">
         <v>20</v>
       </c>
       <c r="B20" s="33" t="s">
@@ -9184,13 +9688,13 @@
       <c r="J20" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K20" s="80" t="s">
+      <c r="K20" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L20" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M20" s="80" t="s">
+      <c r="M20" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N20" s="43" t="s">
@@ -9199,7 +9703,7 @@
       <c r="O20" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="P20" s="81" t="s">
+      <c r="P20" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q20" s="46" t="s">
@@ -9297,8 +9801,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="82">
+    <row r="21" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="80">
         <v>21</v>
       </c>
       <c r="B21" s="33" t="s">
@@ -9328,13 +9832,13 @@
       <c r="J21" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K21" s="80" t="s">
+      <c r="K21" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L21" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M21" s="80" t="s">
+      <c r="M21" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N21" s="43" t="s">
@@ -9343,7 +9847,7 @@
       <c r="O21" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="P21" s="81" t="s">
+      <c r="P21" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q21" s="46" t="s">
@@ -9441,8 +9945,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="82">
+    <row r="22" spans="1:47" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="80">
         <v>22</v>
       </c>
       <c r="B22" s="33" t="s">
@@ -9472,13 +9976,13 @@
       <c r="J22" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K22" s="80" t="s">
+      <c r="K22" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L22" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M22" s="80" t="s">
+      <c r="M22" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N22" s="43" t="s">
@@ -9585,8 +10089,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="82">
+    <row r="23" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="80">
         <v>23</v>
       </c>
       <c r="B23" s="33" t="s">
@@ -9616,13 +10120,13 @@
       <c r="J23" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K23" s="80" t="s">
+      <c r="K23" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L23" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M23" s="80" t="s">
+      <c r="M23" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N23" s="43" t="s">
@@ -9729,8 +10233,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="82">
+    <row r="24" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="80">
         <v>24</v>
       </c>
       <c r="B24" s="33" t="s">
@@ -9760,13 +10264,13 @@
       <c r="J24" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K24" s="80" t="s">
+      <c r="K24" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L24" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M24" s="80" t="s">
+      <c r="M24" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N24" s="43" t="s">
@@ -9873,8 +10377,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="82">
+    <row r="25" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="80">
         <v>25</v>
       </c>
       <c r="B25" s="49" t="s">
@@ -9904,13 +10408,13 @@
       <c r="J25" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K25" s="80" t="s">
+      <c r="K25" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L25" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M25" s="80" t="s">
+      <c r="M25" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N25" s="43" t="s">
@@ -9919,7 +10423,7 @@
       <c r="O25" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="P25" s="81" t="s">
+      <c r="P25" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q25" s="46" t="s">
@@ -10016,8 +10520,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="82">
+    <row r="26" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="80">
         <v>26</v>
       </c>
       <c r="B26" s="49" t="s">
@@ -10047,13 +10551,13 @@
       <c r="J26" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K26" s="80" t="s">
+      <c r="K26" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L26" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M26" s="80" t="s">
+      <c r="M26" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N26" s="43" t="s">
@@ -10062,7 +10566,7 @@
       <c r="O26" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="P26" s="81" t="s">
+      <c r="P26" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q26" s="46" t="s">
@@ -10159,8 +10663,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="82">
+    <row r="27" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="80">
         <v>27</v>
       </c>
       <c r="B27" s="49" t="s">
@@ -10190,13 +10694,13 @@
       <c r="J27" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K27" s="80" t="s">
+      <c r="K27" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L27" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M27" s="80" t="s">
+      <c r="M27" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N27" s="43" t="s">
@@ -10205,7 +10709,7 @@
       <c r="O27" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="P27" s="81" t="s">
+      <c r="P27" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q27" s="46" t="s">
@@ -10302,8 +10806,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="82">
+    <row r="28" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="80">
         <v>28</v>
       </c>
       <c r="B28" s="49" t="s">
@@ -10333,13 +10837,13 @@
       <c r="J28" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K28" s="80" t="s">
+      <c r="K28" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L28" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M28" s="80" t="s">
+      <c r="M28" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N28" s="43" t="s">
@@ -10348,7 +10852,7 @@
       <c r="O28" s="46" t="s">
         <v>273</v>
       </c>
-      <c r="P28" s="81" t="s">
+      <c r="P28" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q28" s="46" t="s">
@@ -10445,8 +10949,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="82">
+    <row r="29" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="80">
         <v>29</v>
       </c>
       <c r="B29" s="49" t="s">
@@ -10476,13 +10980,13 @@
       <c r="J29" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K29" s="80" t="s">
+      <c r="K29" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L29" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M29" s="80" t="s">
+      <c r="M29" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N29" s="43" t="s">
@@ -10491,7 +10995,7 @@
       <c r="O29" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="P29" s="81" t="s">
+      <c r="P29" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q29" s="46" t="s">
@@ -10588,8 +11092,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="82">
+    <row r="30" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="80">
         <v>30</v>
       </c>
       <c r="B30" s="49" t="s">
@@ -10619,13 +11123,13 @@
       <c r="J30" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K30" s="80" t="s">
+      <c r="K30" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L30" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M30" s="80" t="s">
+      <c r="M30" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N30" s="43" t="s">
@@ -10634,7 +11138,7 @@
       <c r="O30" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="P30" s="81" t="s">
+      <c r="P30" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q30" s="46" t="s">
@@ -10731,8 +11235,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="82">
+    <row r="31" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="80">
         <v>31</v>
       </c>
       <c r="B31" s="49" t="s">
@@ -10762,13 +11266,13 @@
       <c r="J31" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K31" s="80" t="s">
+      <c r="K31" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L31" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M31" s="80" t="s">
+      <c r="M31" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N31" s="43" t="s">
@@ -10777,7 +11281,7 @@
       <c r="O31" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="P31" s="81" t="s">
+      <c r="P31" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q31" s="46" t="s">
@@ -10874,8 +11378,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="82">
+    <row r="32" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="80">
         <v>32</v>
       </c>
       <c r="B32" s="49" t="s">
@@ -10905,13 +11409,13 @@
       <c r="J32" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K32" s="80" t="s">
+      <c r="K32" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L32" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M32" s="80" t="s">
+      <c r="M32" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N32" s="43" t="s">
@@ -10920,7 +11424,7 @@
       <c r="O32" s="46" t="s">
         <v>277</v>
       </c>
-      <c r="P32" s="81" t="s">
+      <c r="P32" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q32" s="46" t="s">
@@ -11017,8 +11521,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="82">
+    <row r="33" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="80">
         <v>33</v>
       </c>
       <c r="B33" s="49" t="s">
@@ -11048,13 +11552,13 @@
       <c r="J33" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K33" s="80" t="s">
+      <c r="K33" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L33" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M33" s="80" t="s">
+      <c r="M33" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N33" s="43" t="s">
@@ -11063,7 +11567,7 @@
       <c r="O33" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="P33" s="81" t="s">
+      <c r="P33" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q33" s="46" t="s">
@@ -11160,8 +11664,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="82">
+    <row r="34" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="80">
         <v>34</v>
       </c>
       <c r="B34" s="49" t="s">
@@ -11191,13 +11695,13 @@
       <c r="J34" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K34" s="80" t="s">
+      <c r="K34" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L34" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M34" s="80" t="s">
+      <c r="M34" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N34" s="43" t="s">
@@ -11206,7 +11710,7 @@
       <c r="O34" s="46" t="s">
         <v>279</v>
       </c>
-      <c r="P34" s="81" t="s">
+      <c r="P34" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q34" s="46" t="s">
@@ -11303,8 +11807,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="82">
+    <row r="35" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="80">
         <v>35</v>
       </c>
       <c r="B35" s="49" t="s">
@@ -11334,13 +11838,13 @@
       <c r="J35" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K35" s="80" t="s">
+      <c r="K35" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L35" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M35" s="80" t="s">
+      <c r="M35" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N35" s="43" t="s">
@@ -11349,7 +11853,7 @@
       <c r="O35" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="P35" s="81" t="s">
+      <c r="P35" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q35" s="46" t="s">
@@ -11446,8 +11950,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="82">
+    <row r="36" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="80">
         <v>36</v>
       </c>
       <c r="B36" s="49" t="s">
@@ -11477,13 +11981,13 @@
       <c r="J36" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K36" s="80" t="s">
+      <c r="K36" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L36" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M36" s="80" t="s">
+      <c r="M36" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N36" s="43" t="s">
@@ -11492,7 +11996,7 @@
       <c r="O36" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="P36" s="81" t="s">
+      <c r="P36" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q36" s="46" t="s">
@@ -11589,8 +12093,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="82">
+    <row r="37" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="80">
         <v>37</v>
       </c>
       <c r="B37" s="49" t="s">
@@ -11620,13 +12124,13 @@
       <c r="J37" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K37" s="80" t="s">
+      <c r="K37" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L37" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M37" s="80" t="s">
+      <c r="M37" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N37" s="43" t="s">
@@ -11635,7 +12139,7 @@
       <c r="O37" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="P37" s="81" t="s">
+      <c r="P37" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q37" s="46" t="s">
@@ -11732,8 +12236,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="82">
+    <row r="38" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="80">
         <v>38</v>
       </c>
       <c r="B38" s="49" t="s">
@@ -11763,13 +12267,13 @@
       <c r="J38" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K38" s="80" t="s">
+      <c r="K38" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L38" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M38" s="80" t="s">
+      <c r="M38" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N38" s="43" t="s">
@@ -11778,7 +12282,7 @@
       <c r="O38" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="P38" s="81" t="s">
+      <c r="P38" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q38" s="46" t="s">
@@ -11875,8 +12379,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="82">
+    <row r="39" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="80">
         <v>39</v>
       </c>
       <c r="B39" s="49" t="s">
@@ -11906,13 +12410,13 @@
       <c r="J39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K39" s="80" t="s">
+      <c r="K39" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M39" s="80" t="s">
+      <c r="M39" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N39" s="43" t="s">
@@ -11921,7 +12425,7 @@
       <c r="O39" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="P39" s="81" t="s">
+      <c r="P39" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q39" s="46" t="s">
@@ -12018,8 +12522,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="82">
+    <row r="40" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="80">
         <v>40</v>
       </c>
       <c r="B40" s="49" t="s">
@@ -12049,13 +12553,13 @@
       <c r="J40" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K40" s="80" t="s">
+      <c r="K40" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L40" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M40" s="80" t="s">
+      <c r="M40" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N40" s="43" t="s">
@@ -12064,7 +12568,7 @@
       <c r="O40" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="P40" s="81" t="s">
+      <c r="P40" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q40" s="46" t="s">
@@ -12161,8 +12665,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="82">
+    <row r="41" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="80">
         <v>41</v>
       </c>
       <c r="B41" s="49" t="s">
@@ -12192,13 +12696,13 @@
       <c r="J41" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K41" s="80" t="s">
+      <c r="K41" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L41" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M41" s="80" t="s">
+      <c r="M41" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N41" s="43" t="s">
@@ -12207,7 +12711,7 @@
       <c r="O41" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="P41" s="81" t="s">
+      <c r="P41" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q41" s="46" t="s">
@@ -12304,8 +12808,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="82">
+    <row r="42" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="80">
         <v>42</v>
       </c>
       <c r="B42" s="49" t="s">
@@ -12335,13 +12839,13 @@
       <c r="J42" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K42" s="80" t="s">
+      <c r="K42" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L42" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M42" s="80" t="s">
+      <c r="M42" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N42" s="43" t="s">
@@ -12350,7 +12854,7 @@
       <c r="O42" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="P42" s="81" t="s">
+      <c r="P42" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q42" s="46" t="s">
@@ -12447,8 +12951,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="82">
+    <row r="43" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="80">
         <v>43</v>
       </c>
       <c r="B43" s="49" t="s">
@@ -12478,13 +12982,13 @@
       <c r="J43" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K43" s="80" t="s">
+      <c r="K43" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L43" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M43" s="80" t="s">
+      <c r="M43" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N43" s="43" t="s">
@@ -12493,7 +12997,7 @@
       <c r="O43" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="P43" s="81" t="s">
+      <c r="P43" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q43" s="46" t="s">
@@ -12590,8 +13094,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="82">
+    <row r="44" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="80">
         <v>44</v>
       </c>
       <c r="B44" s="49" t="s">
@@ -12621,13 +13125,13 @@
       <c r="J44" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K44" s="80" t="s">
+      <c r="K44" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L44" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M44" s="80" t="s">
+      <c r="M44" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N44" s="43" t="s">
@@ -12636,7 +13140,7 @@
       <c r="O44" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="P44" s="81" t="s">
+      <c r="P44" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q44" s="46" t="s">
@@ -12733,8 +13237,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="82">
+    <row r="45" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="80">
         <v>45</v>
       </c>
       <c r="B45" s="49" t="s">
@@ -12764,13 +13268,13 @@
       <c r="J45" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K45" s="80" t="s">
+      <c r="K45" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L45" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M45" s="80" t="s">
+      <c r="M45" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N45" s="43" t="s">
@@ -12779,7 +13283,7 @@
       <c r="O45" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="P45" s="81" t="s">
+      <c r="P45" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q45" s="46" t="s">
@@ -12876,8 +13380,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="82">
+    <row r="46" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="80">
         <v>46</v>
       </c>
       <c r="B46" s="49" t="s">
@@ -12907,13 +13411,13 @@
       <c r="J46" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K46" s="80" t="s">
+      <c r="K46" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L46" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M46" s="80" t="s">
+      <c r="M46" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N46" s="43" t="s">
@@ -12922,7 +13426,7 @@
       <c r="O46" s="46" t="s">
         <v>290</v>
       </c>
-      <c r="P46" s="81" t="s">
+      <c r="P46" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q46" s="46" t="s">
@@ -13019,8 +13523,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="82">
+    <row r="47" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="80">
         <v>47</v>
       </c>
       <c r="B47" s="49" t="s">
@@ -13050,13 +13554,13 @@
       <c r="J47" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K47" s="80" t="s">
+      <c r="K47" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L47" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M47" s="80" t="s">
+      <c r="M47" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N47" s="43" t="s">
@@ -13065,7 +13569,7 @@
       <c r="O47" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="P47" s="81" t="s">
+      <c r="P47" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q47" s="46" t="s">
@@ -13162,8 +13666,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="82">
+    <row r="48" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="80">
         <v>48</v>
       </c>
       <c r="B48" s="49" t="s">
@@ -13193,13 +13697,13 @@
       <c r="J48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K48" s="80" t="s">
+      <c r="K48" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M48" s="80" t="s">
+      <c r="M48" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N48" s="43" t="s">
@@ -13208,7 +13712,7 @@
       <c r="O48" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="P48" s="81" t="s">
+      <c r="P48" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q48" s="46" t="s">
@@ -13305,8 +13809,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="82">
+    <row r="49" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="80">
         <v>49</v>
       </c>
       <c r="B49" s="49" t="s">
@@ -13336,13 +13840,13 @@
       <c r="J49" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K49" s="80" t="s">
+      <c r="K49" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L49" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M49" s="80" t="s">
+      <c r="M49" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N49" s="43" t="s">
@@ -13351,7 +13855,7 @@
       <c r="O49" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="P49" s="81" t="s">
+      <c r="P49" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q49" s="46" t="s">
@@ -13448,8 +13952,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="82">
+    <row r="50" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="80">
         <v>50</v>
       </c>
       <c r="B50" s="49" t="s">
@@ -13479,13 +13983,13 @@
       <c r="J50" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K50" s="80" t="s">
+      <c r="K50" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L50" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M50" s="80" t="s">
+      <c r="M50" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N50" s="43" t="s">
@@ -13494,7 +13998,7 @@
       <c r="O50" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="P50" s="81" t="s">
+      <c r="P50" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q50" s="46" t="s">
@@ -13591,8 +14095,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="82">
+    <row r="51" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="80">
         <v>51</v>
       </c>
       <c r="B51" s="49" t="s">
@@ -13622,13 +14126,13 @@
       <c r="J51" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K51" s="80" t="s">
+      <c r="K51" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L51" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M51" s="80" t="s">
+      <c r="M51" s="78" t="s">
         <v>1</v>
       </c>
       <c r="N51" s="43" t="s">
@@ -13637,7 +14141,7 @@
       <c r="O51" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="P51" s="81" t="s">
+      <c r="P51" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="46" t="s">
@@ -13734,8 +14238,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="82">
+    <row r="52" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="80">
         <v>52</v>
       </c>
       <c r="B52" s="49" t="s">
@@ -13780,7 +14284,7 @@
       <c r="O52" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="P52" s="81" t="s">
+      <c r="P52" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q52" s="46" t="s">
@@ -13877,8 +14381,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="82">
+    <row r="53" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="80">
         <v>53</v>
       </c>
       <c r="B53" s="49" t="s">
@@ -13923,7 +14427,7 @@
       <c r="O53" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="P53" s="81" t="s">
+      <c r="P53" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q53" s="46" t="s">
@@ -14020,8 +14524,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="82">
+    <row r="54" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="80">
         <v>54</v>
       </c>
       <c r="B54" s="49" t="s">
@@ -14066,7 +14570,7 @@
       <c r="O54" s="53" t="s">
         <v>298</v>
       </c>
-      <c r="P54" s="81" t="s">
+      <c r="P54" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q54" s="46" t="s">
@@ -14163,8 +14667,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="82">
+    <row r="55" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="80">
         <v>55</v>
       </c>
       <c r="B55" s="49" t="s">
@@ -14209,7 +14713,7 @@
       <c r="O55" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="P55" s="81" t="s">
+      <c r="P55" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q55" s="46" t="s">
@@ -14306,8 +14810,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="82">
+    <row r="56" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="80">
         <v>56</v>
       </c>
       <c r="B56" s="49" t="s">
@@ -14352,7 +14856,7 @@
       <c r="O56" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="P56" s="81" t="s">
+      <c r="P56" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q56" s="46" t="s">
@@ -14449,8 +14953,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="82">
+    <row r="57" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="80">
         <v>57</v>
       </c>
       <c r="B57" s="49" t="s">
@@ -14495,7 +14999,7 @@
       <c r="O57" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="P57" s="81" t="s">
+      <c r="P57" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q57" s="46" t="s">
@@ -14592,8 +15096,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="82">
+    <row r="58" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="80">
         <v>58</v>
       </c>
       <c r="B58" s="49" t="s">
@@ -14638,7 +15142,7 @@
       <c r="O58" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="P58" s="81" t="s">
+      <c r="P58" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q58" s="46" t="s">
@@ -14735,8 +15239,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="82">
+    <row r="59" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="80">
         <v>59</v>
       </c>
       <c r="B59" s="49" t="s">
@@ -14781,7 +15285,7 @@
       <c r="O59" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="P59" s="81" t="s">
+      <c r="P59" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q59" s="46" t="s">
@@ -14878,8 +15382,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="82">
+    <row r="60" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="80">
         <v>60</v>
       </c>
       <c r="B60" s="49" t="s">
@@ -14924,7 +15428,7 @@
       <c r="O60" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="P60" s="81" t="s">
+      <c r="P60" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q60" s="46" t="s">
@@ -15021,8 +15525,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="82">
+    <row r="61" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="80">
         <v>61</v>
       </c>
       <c r="B61" s="49" t="s">
@@ -15067,7 +15571,7 @@
       <c r="O61" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="P61" s="81" t="s">
+      <c r="P61" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q61" s="46" t="s">
@@ -15164,8 +15668,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="82">
+    <row r="62" spans="1:47" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="80">
         <v>62</v>
       </c>
       <c r="B62" s="49" t="s">
@@ -15210,7 +15714,7 @@
       <c r="O62" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="P62" s="81" t="s">
+      <c r="P62" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q62" s="46" t="s">
@@ -15307,118 +15811,118 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="82">
+    <row r="63" spans="1:47" s="89" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="80">
         <v>63</v>
       </c>
-      <c r="B63" s="83" t="s">
+      <c r="B63" s="81" t="s">
+        <v>396</v>
+      </c>
+      <c r="C63" s="91" t="s">
+        <v>431</v>
+      </c>
+      <c r="D63" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K63" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="L63" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="M63" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="N63" s="84" t="s">
+        <v>140</v>
+      </c>
+      <c r="O63" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="P63" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R63" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S63" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T63" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="U63" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="V63" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="W63" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="X63" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD63" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="85" t="s">
+        <v>398</v>
+      </c>
+      <c r="AG63" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="AH63" s="85" t="s">
         <v>400</v>
       </c>
-      <c r="C63" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="D63" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K63" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="L63" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="M63" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="N63" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="O63" s="53" t="s">
+      <c r="AI63" s="53" t="s">
         <v>401</v>
       </c>
-      <c r="P63" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R63" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S63" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="T63" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="U63" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="V63" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="W63" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="X63" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y63" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD63" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE63" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF63" s="87" t="s">
-        <v>402</v>
-      </c>
-      <c r="AG63" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="AH63" s="87" t="s">
-        <v>404</v>
-      </c>
-      <c r="AI63" s="53" t="s">
-        <v>405</v>
-      </c>
-      <c r="AJ63" s="88" t="str">
+      <c r="AJ63" s="86" t="str">
         <f t="shared" ref="AJ63:AJ67" si="2">IF(AK63="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="AK63" s="89" t="s">
-        <v>406</v>
+      <c r="AK63" s="87" t="s">
+        <v>402</v>
       </c>
       <c r="AL63" s="30" t="s">
         <v>1</v>
@@ -15451,26 +15955,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="82">
+    <row r="64" spans="1:47" s="89" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="80">
         <v>64</v>
       </c>
-      <c r="B64" s="83" t="s">
-        <v>407</v>
-      </c>
-      <c r="C64" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="D64" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="85" t="s">
+      <c r="B64" s="81" t="s">
+        <v>403</v>
+      </c>
+      <c r="C64" s="91" t="s">
+        <v>431</v>
+      </c>
+      <c r="D64" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H64" s="30" t="s">
@@ -15482,22 +15986,22 @@
       <c r="J64" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K64" s="80" t="s">
+      <c r="K64" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L64" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M64" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="N64" s="86" t="s">
+      <c r="M64" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="N64" s="84" t="s">
         <v>140</v>
       </c>
       <c r="O64" s="53" t="s">
-        <v>408</v>
-      </c>
-      <c r="P64" s="81" t="s">
+        <v>404</v>
+      </c>
+      <c r="P64" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q64" s="46" t="s">
@@ -15509,13 +16013,13 @@
       <c r="S64" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="T64" s="87" t="s">
+      <c r="T64" s="85" t="s">
         <v>1</v>
       </c>
       <c r="U64" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="V64" s="90" t="s">
+      <c r="V64" s="88" t="s">
         <v>1</v>
       </c>
       <c r="W64" s="53" t="s">
@@ -15545,24 +16049,24 @@
       <c r="AE64" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AF64" s="87" t="s">
-        <v>402</v>
+      <c r="AF64" s="85" t="s">
+        <v>398</v>
       </c>
       <c r="AG64" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="AH64" s="87" t="s">
-        <v>404</v>
+        <v>399</v>
+      </c>
+      <c r="AH64" s="85" t="s">
+        <v>400</v>
       </c>
       <c r="AI64" s="53" t="s">
-        <v>409</v>
-      </c>
-      <c r="AJ64" s="88" t="str">
+        <v>405</v>
+      </c>
+      <c r="AJ64" s="86" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
-      <c r="AK64" s="89" t="s">
-        <v>410</v>
+      <c r="AK64" s="87" t="s">
+        <v>406</v>
       </c>
       <c r="AL64" s="30" t="s">
         <v>1</v>
@@ -15595,26 +16099,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="82">
+    <row r="65" spans="1:47" s="89" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="80">
         <v>65</v>
       </c>
-      <c r="B65" s="83" t="s">
-        <v>411</v>
-      </c>
-      <c r="C65" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="D65" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="85" t="s">
+      <c r="B65" s="81" t="s">
+        <v>407</v>
+      </c>
+      <c r="C65" s="91" t="s">
+        <v>431</v>
+      </c>
+      <c r="D65" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H65" s="30" t="s">
@@ -15626,22 +16130,22 @@
       <c r="J65" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K65" s="80" t="s">
+      <c r="K65" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L65" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M65" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="N65" s="86" t="s">
+      <c r="M65" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="N65" s="84" t="s">
         <v>140</v>
       </c>
       <c r="O65" s="53" t="s">
-        <v>412</v>
-      </c>
-      <c r="P65" s="81" t="s">
+        <v>408</v>
+      </c>
+      <c r="P65" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q65" s="46" t="s">
@@ -15653,13 +16157,13 @@
       <c r="S65" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="T65" s="87" t="s">
+      <c r="T65" s="85" t="s">
         <v>1</v>
       </c>
       <c r="U65" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="V65" s="90" t="s">
+      <c r="V65" s="88" t="s">
         <v>1</v>
       </c>
       <c r="W65" s="53" t="s">
@@ -15689,24 +16193,24 @@
       <c r="AE65" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AF65" s="87" t="s">
-        <v>402</v>
+      <c r="AF65" s="85" t="s">
+        <v>398</v>
       </c>
       <c r="AG65" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="AH65" s="87" t="s">
-        <v>404</v>
+        <v>399</v>
+      </c>
+      <c r="AH65" s="85" t="s">
+        <v>400</v>
       </c>
       <c r="AI65" s="53" t="s">
-        <v>413</v>
-      </c>
-      <c r="AJ65" s="88" t="str">
+        <v>409</v>
+      </c>
+      <c r="AJ65" s="86" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
-      <c r="AK65" s="89" t="s">
-        <v>414</v>
+      <c r="AK65" s="87" t="s">
+        <v>410</v>
       </c>
       <c r="AL65" s="30" t="s">
         <v>1</v>
@@ -15739,26 +16243,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="82">
+    <row r="66" spans="1:47" s="89" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="80">
         <v>66</v>
       </c>
-      <c r="B66" s="83" t="s">
-        <v>415</v>
-      </c>
-      <c r="C66" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="D66" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="85" t="s">
+      <c r="B66" s="81" t="s">
+        <v>411</v>
+      </c>
+      <c r="C66" s="91" t="s">
+        <v>431</v>
+      </c>
+      <c r="D66" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H66" s="30" t="s">
@@ -15770,22 +16274,22 @@
       <c r="J66" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K66" s="80" t="s">
+      <c r="K66" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L66" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M66" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="N66" s="86" t="s">
+      <c r="M66" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="N66" s="84" t="s">
         <v>140</v>
       </c>
       <c r="O66" s="53" t="s">
-        <v>416</v>
-      </c>
-      <c r="P66" s="81" t="s">
+        <v>412</v>
+      </c>
+      <c r="P66" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q66" s="46" t="s">
@@ -15797,13 +16301,13 @@
       <c r="S66" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="T66" s="87" t="s">
+      <c r="T66" s="85" t="s">
         <v>1</v>
       </c>
       <c r="U66" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="V66" s="90" t="s">
+      <c r="V66" s="88" t="s">
         <v>1</v>
       </c>
       <c r="W66" s="53" t="s">
@@ -15833,24 +16337,24 @@
       <c r="AE66" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AF66" s="87" t="s">
-        <v>402</v>
+      <c r="AF66" s="85" t="s">
+        <v>398</v>
       </c>
       <c r="AG66" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="AH66" s="87" t="s">
-        <v>404</v>
+        <v>399</v>
+      </c>
+      <c r="AH66" s="85" t="s">
+        <v>400</v>
       </c>
       <c r="AI66" s="53" t="s">
-        <v>417</v>
-      </c>
-      <c r="AJ66" s="88" t="str">
+        <v>413</v>
+      </c>
+      <c r="AJ66" s="86" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
-      <c r="AK66" s="89" t="s">
-        <v>418</v>
+      <c r="AK66" s="87" t="s">
+        <v>414</v>
       </c>
       <c r="AL66" s="30" t="s">
         <v>1</v>
@@ -15883,26 +16387,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:47" s="91" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="82">
+    <row r="67" spans="1:47" s="89" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="80">
         <v>67</v>
       </c>
-      <c r="B67" s="83" t="s">
-        <v>419</v>
-      </c>
-      <c r="C67" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="D67" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="85" t="s">
+      <c r="B67" s="81" t="s">
+        <v>415</v>
+      </c>
+      <c r="C67" s="91" t="s">
+        <v>431</v>
+      </c>
+      <c r="D67" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H67" s="30" t="s">
@@ -15914,22 +16418,22 @@
       <c r="J67" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="K67" s="80" t="s">
+      <c r="K67" s="78" t="s">
         <v>1</v>
       </c>
       <c r="L67" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="M67" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="N67" s="86" t="s">
+      <c r="M67" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="N67" s="84" t="s">
         <v>140</v>
       </c>
       <c r="O67" s="53" t="s">
-        <v>420</v>
-      </c>
-      <c r="P67" s="81" t="s">
+        <v>416</v>
+      </c>
+      <c r="P67" s="79" t="s">
         <v>1</v>
       </c>
       <c r="Q67" s="46" t="s">
@@ -15941,13 +16445,13 @@
       <c r="S67" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="T67" s="87" t="s">
+      <c r="T67" s="85" t="s">
         <v>1</v>
       </c>
       <c r="U67" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="V67" s="90" t="s">
+      <c r="V67" s="88" t="s">
         <v>1</v>
       </c>
       <c r="W67" s="53" t="s">
@@ -15977,24 +16481,24 @@
       <c r="AE67" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AF67" s="87" t="s">
-        <v>402</v>
+      <c r="AF67" s="85" t="s">
+        <v>398</v>
       </c>
       <c r="AG67" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="AH67" s="87" t="s">
-        <v>404</v>
+        <v>399</v>
+      </c>
+      <c r="AH67" s="85" t="s">
+        <v>400</v>
       </c>
       <c r="AI67" s="53" t="s">
-        <v>421</v>
-      </c>
-      <c r="AJ67" s="88" t="str">
+        <v>417</v>
+      </c>
+      <c r="AJ67" s="86" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
-      <c r="AK67" s="89" t="s">
-        <v>422</v>
+      <c r="AK67" s="87" t="s">
+        <v>418</v>
       </c>
       <c r="AL67" s="30" t="s">
         <v>1</v>
@@ -16033,50 +16537,50 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:I2 B3:I17 B18 B19:I19 B20:B21 B22:I62 A68:AS1048576 L1:Y15 Z1:AA17 AB1:AS62 AT1:AU1048576 A3:A67 T16:Y17 R16:S18 N22:Y31 Z22:AA62 L32:Y62 AL63:AS67 AV68:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B62 B68:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63:B67">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:I18 AV1:XFD62 L16:Q17 N18:Q18 T18:AA18">
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:I21 N19:AA21">
-    <cfRule type="cellIs" dxfId="5" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:I67">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K67">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18:M67">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P63:AE67">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16087,15 +16591,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.3046875" customWidth="1"/>
-    <col min="4" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -16106,7 +16610,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -16117,7 +16621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -16128,7 +16632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -16139,7 +16643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -16150,7 +16654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -16161,7 +16665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -16172,7 +16676,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -16183,7 +16687,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -16194,7 +16698,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -16205,7 +16709,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -16216,7 +16720,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -16227,7 +16731,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -16238,7 +16742,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -16249,7 +16753,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -16260,47 +16764,47 @@
         <v>307</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C16" s="29" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C17" s="29" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="18" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C18" s="29" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C19" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C20" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C21" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C22" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C23" s="64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C24" s="64" t="s">
         <v>1</v>
       </c>

--- a/Versão5/PRO/Ontologia_Cromatica.xlsx
+++ b/Versão5/PRO/Ontologia_Cromatica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3041F4EF-866C-4F65-BB50-841073AE8C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7568A3-5308-4A6B-8BB4-0C1EE6EB3FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3702" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="489">
   <si>
     <t>Key</t>
   </si>
@@ -1427,12 +1427,6 @@
     <t>Autor</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -1452,21 +1446,6 @@
   </si>
   <si>
     <t>Escola Politécnica da UFRJ</t>
-  </si>
-  <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>DataHora</t>
@@ -2591,6 +2570,165 @@
   </si>
   <si>
     <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
@@ -2600,7 +2738,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2773,8 +2911,16 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2943,6 +3089,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -3005,10 +3163,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3289,91 +3448,39 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -3559,6 +3666,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3892,61 +4007,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="54" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="96" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>251</v>
+      <c r="C4" s="53" t="s">
+        <v>244</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="14" t="str">
@@ -3954,11 +4069,11 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>54</v>
       </c>
       <c r="B6" s="14" t="str">
@@ -3966,234 +4081,496 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>251</v>
+      <c r="C9" s="53" t="s">
+        <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>66</v>
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>57</v>
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>437</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>58</v>
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>438</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>67</v>
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>439</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>68</v>
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>440</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>69</v>
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>441</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>70</v>
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>442</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>59</v>
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>71</v>
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46274.374587268518</v>
+        <v>46276.434293402781</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>254</v>
+    <row r="20" spans="1:3" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>247</v>
       </c>
       <c r="B20" s="55" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>255</v>
+    <row r="21" spans="1:3" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="B21" s="55" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>248</v>
+    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of chromatic elements</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>253</v>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B27" s="97" t="s">
+        <v>466</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="B28" s="98" t="s">
+        <v>467</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="B29" s="98" t="s">
+        <v>468</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="B30" s="99" t="s">
+        <v>469</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="B31" s="100" t="s">
+        <v>470</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="B32" s="100" t="s">
+        <v>471</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B33" s="100" t="s">
+        <v>472</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="B34" s="101" t="s">
+        <v>473</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="B35" s="101" t="s">
+        <v>474</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="B36" s="100" t="s">
+        <v>475</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="101" t="s">
+        <v>476</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="B38" s="100" t="s">
+        <v>477</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="B39" s="102" t="s">
+        <v>478</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B40" s="102" t="s">
+        <v>479</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="B41" s="103" t="s">
+        <v>480</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="B42" s="104" t="s">
+        <v>481</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="B43" s="104" t="s">
+        <v>482</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="B44" s="104" t="s">
+        <v>483</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="B45" s="104" t="s">
+        <v>484</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="B46" s="104" t="s">
+        <v>485</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="B47" s="104" t="s">
+        <v>486</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="B48" s="104" t="s">
+        <v>487</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="B49" s="104" t="s">
+        <v>488</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{5C8DEE10-7DCE-4653-8847-495084D8DCC1}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{1DC3ACA3-9384-4849-819C-4CC4EEEC0135}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{854C52FE-54A1-484E-A900-6392630140F6}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{A56EABA6-F078-4BBC-AD42-1BB1A5E9A29D}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{D89F8113-BDAF-480E-B79B-14A8B2660EE9}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{D40E3883-F280-4F40-84D4-40844D8CD150}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{B52EA2CD-2D03-4DD1-9F15-226878E5EE00}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -4233,22 +4610,22 @@
   <sheetData>
     <row r="1" spans="1:30" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>84</v>
-      </c>
       <c r="F1" s="22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G1" s="63" t="s">
         <v>39</v>
@@ -4278,49 +4655,49 @@
         <v>44</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="R1" s="51" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="S1" s="94" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="U1" s="24" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="V1" s="25" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="W1" s="24" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="X1" s="67" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="24" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="Z1" s="24" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AA1" s="24" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AB1" s="24" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AC1" s="24" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AD1" s="24" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4328,19 +4705,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D2" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E2" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F2" s="89" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G2" s="64" t="s">
         <v>1</v>
@@ -4355,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="65" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="L2" s="58" t="str">
         <f>_xlfn.CONCAT(C2)</f>
@@ -4374,13 +4751,13 @@
         <v>Cyan</v>
       </c>
       <c r="P2" s="58" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="Q2" s="58" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="R2" s="52" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="S2" s="95" t="s">
         <v>1</v>
@@ -4398,7 +4775,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W2" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X2" s="68" t="str">
         <f t="shared" ref="X2:X19" si="2">CONCATENATE("Key-CROMA-",A2)</f>
@@ -4428,19 +4805,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D3" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F3" s="89" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G3" s="64" t="s">
         <v>1</v>
@@ -4455,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="65" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="L3" s="58" t="str">
         <f>_xlfn.CONCAT(C3)</f>
@@ -4474,13 +4851,13 @@
         <v>Magenta</v>
       </c>
       <c r="P3" s="58" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="Q3" s="58" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="R3" s="52" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="S3" s="95" t="s">
         <v>1</v>
@@ -4498,7 +4875,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W3" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X3" s="68" t="str">
         <f t="shared" si="2"/>
@@ -4528,19 +4905,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D4" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E4" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F4" s="89" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G4" s="64" t="s">
         <v>1</v>
@@ -4555,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="65" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L4" s="58" t="str">
         <f>_xlfn.CONCAT(C4)</f>
@@ -4574,13 +4951,13 @@
         <v>Yellow</v>
       </c>
       <c r="P4" s="58" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q4" s="58" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="R4" s="52" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="S4" s="95" t="s">
         <v>1</v>
@@ -4598,7 +4975,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W4" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X4" s="68" t="str">
         <f t="shared" si="2"/>
@@ -4628,19 +5005,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F5" s="89" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G5" s="64" t="s">
         <v>1</v>
@@ -4655,7 +5032,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="65" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L5" s="58" t="str">
         <f t="shared" ref="L5:L20" si="3">_xlfn.CONCAT(C5)</f>
@@ -4674,13 +5051,13 @@
         <v>Black</v>
       </c>
       <c r="P5" s="58" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Q5" s="58" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="R5" s="52" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="S5" s="95" t="s">
         <v>1</v>
@@ -4698,7 +5075,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W5" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X5" s="68" t="str">
         <f t="shared" si="2"/>
@@ -4728,19 +5105,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E6" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F6" s="89" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G6" s="64" t="s">
         <v>1</v>
@@ -4755,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="65" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L6" s="58" t="str">
         <f>_xlfn.CONCAT(C6)</f>
@@ -4774,13 +5151,13 @@
         <v>Red</v>
       </c>
       <c r="P6" s="58" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="Q6" s="58" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="R6" s="52" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="S6" s="95" t="s">
         <v>1</v>
@@ -4798,7 +5175,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W6" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X6" s="68" t="str">
         <f t="shared" si="2"/>
@@ -4828,19 +5205,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F7" s="89" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G7" s="64" t="s">
         <v>1</v>
@@ -4855,7 +5232,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="65" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="L7" s="58" t="str">
         <f>_xlfn.CONCAT(C7)</f>
@@ -4874,13 +5251,13 @@
         <v>Green</v>
       </c>
       <c r="P7" s="58" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="Q7" s="58" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="R7" s="52" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="S7" s="95" t="s">
         <v>1</v>
@@ -4898,7 +5275,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W7" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X7" s="68" t="str">
         <f t="shared" si="2"/>
@@ -4928,19 +5305,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E8" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G8" s="64" t="s">
         <v>1</v>
@@ -4955,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="65" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="L8" s="58" t="str">
         <f>_xlfn.CONCAT(C8)</f>
@@ -4974,13 +5351,13 @@
         <v>Blue</v>
       </c>
       <c r="P8" s="58" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="Q8" s="58" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="R8" s="52" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="S8" s="95" t="s">
         <v>1</v>
@@ -4998,7 +5375,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W8" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X8" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5028,19 +5405,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C9" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E9" s="87" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F9" s="89" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G9" s="64" t="s">
         <v>1</v>
@@ -5055,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="65" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="L9" s="58" t="str">
         <f t="shared" ref="L9:L11" si="4">_xlfn.CONCAT(C9)</f>
@@ -5074,13 +5451,13 @@
         <v>Alfa</v>
       </c>
       <c r="P9" s="58" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="Q9" s="58" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="R9" s="52" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="S9" s="95" t="s">
         <v>1</v>
@@ -5098,7 +5475,7 @@
         <v>Canal.de.Cor</v>
       </c>
       <c r="W9" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X9" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5128,19 +5505,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C10" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F10" s="91" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G10" s="64" t="s">
         <v>1</v>
@@ -5155,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="66" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="L10" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5174,13 +5551,13 @@
         <v>CMY</v>
       </c>
       <c r="P10" s="59" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Q10" s="58" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="R10" s="52" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="S10" s="95" t="s">
         <v>1</v>
@@ -5198,7 +5575,7 @@
         <v>Cor.Digital</v>
       </c>
       <c r="W10" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X10" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5228,19 +5605,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D11" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E11" s="90" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F11" s="91" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G11" s="64" t="s">
         <v>1</v>
@@ -5255,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L11" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5274,13 +5651,13 @@
         <v>CMYB</v>
       </c>
       <c r="P11" s="59" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="Q11" s="58" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="R11" s="52" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="S11" s="95" t="s">
         <v>1</v>
@@ -5298,7 +5675,7 @@
         <v>Cor.Digital</v>
       </c>
       <c r="W11" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X11" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5328,19 +5705,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E12" s="90" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F12" s="91" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G12" s="64" t="s">
         <v>1</v>
@@ -5355,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="66" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="L12" s="59" t="str">
         <f t="shared" si="3"/>
@@ -5374,13 +5751,13 @@
         <v>RGB</v>
       </c>
       <c r="P12" s="59" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="Q12" s="58" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="R12" s="52" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="S12" s="95" t="s">
         <v>1</v>
@@ -5398,7 +5775,7 @@
         <v>Cor.Digital</v>
       </c>
       <c r="W12" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X12" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5428,19 +5805,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E13" s="90" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F13" s="91" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G13" s="64" t="s">
         <v>1</v>
@@ -5455,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="66" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="L13" s="59" t="str">
         <f t="shared" si="3"/>
@@ -5474,13 +5851,13 @@
         <v>RGBA</v>
       </c>
       <c r="P13" s="59" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="Q13" s="58" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="R13" s="52" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="S13" s="95" t="s">
         <v>1</v>
@@ -5498,7 +5875,7 @@
         <v>Cor.Digital</v>
       </c>
       <c r="W13" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X13" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5528,19 +5905,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E14" s="90" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F14" s="91" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G14" s="64" t="s">
         <v>1</v>
@@ -5574,13 +5951,13 @@
         <v>Hue</v>
       </c>
       <c r="P14" s="59" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="Q14" s="58" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="R14" s="52" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="S14" s="95" t="s">
         <v>1</v>
@@ -5598,7 +5975,7 @@
         <v>Munsell</v>
       </c>
       <c r="W14" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X14" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5628,19 +6005,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E15" s="90" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F15" s="91" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G15" s="64" t="s">
         <v>1</v>
@@ -5674,13 +6051,13 @@
         <v>Luminosidade</v>
       </c>
       <c r="P15" s="59" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Q15" s="58" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="R15" s="52" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="S15" s="95" t="s">
         <v>1</v>
@@ -5698,7 +6075,7 @@
         <v>Munsell</v>
       </c>
       <c r="W15" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X15" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5728,19 +6105,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E16" s="90" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F16" s="91" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G16" s="64" t="s">
         <v>1</v>
@@ -5774,13 +6151,13 @@
         <v>Croma</v>
       </c>
       <c r="P16" s="59" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="R16" s="52" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="S16" s="95" t="s">
         <v>1</v>
@@ -5798,7 +6175,7 @@
         <v>Munsell</v>
       </c>
       <c r="W16" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X16" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5828,19 +6205,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C17" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E17" s="90" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F17" s="91" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G17" s="64" t="s">
         <v>1</v>
@@ -5874,13 +6251,13 @@
         <v>Cor.Munsell</v>
       </c>
       <c r="P17" s="59" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="Q17" s="58" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="R17" s="52" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="S17" s="95" t="s">
         <v>1</v>
@@ -5898,7 +6275,7 @@
         <v>Munsell</v>
       </c>
       <c r="W17" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X17" s="68" t="str">
         <f t="shared" si="2"/>
@@ -5928,19 +6305,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C18" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D18" s="90" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E18" s="90" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F18" s="91" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G18" s="64" t="s">
         <v>1</v>
@@ -5974,13 +6351,13 @@
         <v xml:space="preserve">Cor.Pantone </v>
       </c>
       <c r="P18" s="59" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="Q18" s="58" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="R18" s="52" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="S18" s="95" t="s">
         <v>1</v>
@@ -5998,7 +6375,7 @@
         <v>Pantone</v>
       </c>
       <c r="W18" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X18" s="68" t="str">
         <f t="shared" si="2"/>
@@ -6028,19 +6405,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D19" s="90" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E19" s="90" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F19" s="91" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G19" s="64" t="s">
         <v>1</v>
@@ -6074,13 +6451,13 @@
         <v xml:space="preserve">Cor.Dnit </v>
       </c>
       <c r="P19" s="59" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Q19" s="58" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="R19" s="52" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="S19" s="95" t="s">
         <v>1</v>
@@ -6098,7 +6475,7 @@
         <v>DNIT</v>
       </c>
       <c r="W19" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X19" s="68" t="str">
         <f t="shared" si="2"/>
@@ -6128,19 +6505,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E20" s="92" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F20" s="90" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="G20" s="64" t="s">
         <v>1</v>
@@ -6174,13 +6551,13 @@
         <v>Cor</v>
       </c>
       <c r="P20" s="59" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="Q20" s="59" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="R20" s="58" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="S20" s="84" t="s">
         <v>1</v>
@@ -6198,10 +6575,10 @@
         <v>Cores</v>
       </c>
       <c r="W20" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X20" s="68" t="str">
-        <f t="shared" ref="X20:X25" si="7">CONCATENATE("Key-CROMA-",A20)</f>
+        <f t="shared" ref="X20" si="7">CONCATENATE("Key-CROMA-",A20)</f>
         <v>Key-CROMA-20</v>
       </c>
       <c r="Y20" s="70" t="s">
@@ -6228,19 +6605,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C21" s="93" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D21" s="93" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E21" s="93" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F21" s="93" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="G21" s="60" t="s">
         <v>1</v>
@@ -6274,13 +6651,13 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="R21" s="52" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="S21" s="84" t="s">
         <v>1</v>
@@ -6298,7 +6675,7 @@
         <v>API Método</v>
       </c>
       <c r="W21" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X21" s="68" t="str">
         <f t="shared" ref="X21:X25" si="11">CONCATENATE("Key-CROMA-",A21)</f>
@@ -6328,19 +6705,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C22" s="93" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D22" s="93" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E22" s="93" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F22" s="93" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G22" s="60" t="s">
         <v>1</v>
@@ -6374,13 +6751,13 @@
         <v>Função Global</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="R22" s="52" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="S22" s="84" t="s">
         <v>1</v>
@@ -6398,7 +6775,7 @@
         <v>API Método</v>
       </c>
       <c r="W22" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X22" s="68" t="str">
         <f t="shared" si="11"/>
@@ -6428,19 +6805,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C23" s="93" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D23" s="93" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E23" s="93" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F23" s="93" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G23" s="60" t="s">
         <v>1</v>
@@ -6474,13 +6851,13 @@
         <v>Função Local</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="R23" s="52" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="S23" s="84" t="s">
         <v>1</v>
@@ -6498,7 +6875,7 @@
         <v>API Método</v>
       </c>
       <c r="W23" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X23" s="68" t="str">
         <f t="shared" si="11"/>
@@ -6528,19 +6905,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C24" s="93" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D24" s="93" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E24" s="93" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F24" s="93" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="G24" s="60" t="s">
         <v>1</v>
@@ -6574,13 +6951,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="R24" s="52" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="S24" s="84" t="s">
         <v>1</v>
@@ -6598,7 +6975,7 @@
         <v>API Método</v>
       </c>
       <c r="W24" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X24" s="68" t="str">
         <f t="shared" si="11"/>
@@ -6628,19 +7005,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C25" s="93" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D25" s="93" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E25" s="93" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F25" s="93" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="G25" s="60" t="s">
         <v>1</v>
@@ -6674,13 +7051,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="R25" s="52" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="S25" s="84" t="s">
         <v>1</v>
@@ -6698,7 +7075,7 @@
         <v>API Método Visual</v>
       </c>
       <c r="W25" s="52" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X25" s="68" t="str">
         <f t="shared" si="11"/>
@@ -6726,39 +7103,39 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B20 A21:A25">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:J1 C2:F19 T1:AD1 L2:Q19 T2:W19 W20:W25">
-    <cfRule type="cellIs" dxfId="31" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="36" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20">
-    <cfRule type="cellIs" dxfId="30" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F19 F26:F1048576">
-    <cfRule type="duplicateValues" dxfId="28" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21:F25">
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q1 K2:K13">
-    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R19">
-    <cfRule type="cellIs" dxfId="24" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F25">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6912,7 +7289,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6936,10 +7313,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6955,7 +7332,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7018,7 +7395,7 @@
   <sheetData>
     <row r="1" spans="1:47" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>49</v>
@@ -7030,133 +7407,133 @@
         <v>48</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J1" s="50" t="s">
         <v>48</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L1" s="50" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="R1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="S1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="T1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="U1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="V1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="W1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="X1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="Y1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="Z1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AA1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AB1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AC1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AD1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AE1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AF1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AG1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AH1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AI1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AJ1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AK1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AL1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AM1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AN1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AO1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AP1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AQ1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AR1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AS1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AT1" s="28" t="s">
         <v>48</v>
       </c>
       <c r="AU1" s="28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:47" s="37" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7164,10 +7541,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>1</v>
@@ -7176,16 +7553,16 @@
         <v>1</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G2" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I2" s="29" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J2" s="40" t="s">
         <v>1</v>
@@ -7200,13 +7577,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q2" s="42">
         <v>255</v>
@@ -7308,10 +7685,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D3" s="27" t="s">
         <v>1</v>
@@ -7320,16 +7697,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J3" s="40" t="s">
         <v>1</v>
@@ -7344,13 +7721,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="Q3" s="42">
         <v>255</v>
@@ -7452,10 +7829,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D4" s="27" t="s">
         <v>1</v>
@@ -7464,16 +7841,16 @@
         <v>1</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J4" s="40" t="s">
         <v>1</v>
@@ -7488,13 +7865,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O4" s="42" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="Q4" s="42">
         <v>255</v>
@@ -7596,10 +7973,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>1</v>
@@ -7614,10 +7991,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J5" s="40" t="s">
         <v>1</v>
@@ -7632,13 +8009,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O5" s="42" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P5" s="39" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="Q5" s="42">
         <v>255</v>
@@ -7740,10 +8117,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D6" s="27" t="s">
         <v>1</v>
@@ -7752,10 +8129,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>1</v>
@@ -7776,25 +8153,25 @@
         <v>1</v>
       </c>
       <c r="N6" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O6" s="42" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q6" s="42">
         <v>255</v>
       </c>
       <c r="R6" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S6" s="42">
         <v>0</v>
       </c>
       <c r="T6" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U6" s="42">
         <v>0</v>
@@ -7806,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y6" s="42" t="str">
         <f t="shared" ref="Y6:Y15" si="0">IF(OR(X6="cor.rgb",X6="cor.cmy",X6="cor.rgba",X6="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q6,".",S6,".",U6,".",W6,""""), ".null",""), X6)</f>
@@ -7884,10 +8261,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>1</v>
@@ -7896,10 +8273,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>1</v>
@@ -7920,25 +8297,25 @@
         <v>1</v>
       </c>
       <c r="N7" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O7" s="42" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="P7" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q7" s="42">
         <v>0</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S7" s="42">
         <v>255</v>
       </c>
       <c r="T7" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U7" s="42">
         <v>0</v>
@@ -7950,7 +8327,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y7" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8028,10 +8405,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D8" s="27" t="s">
         <v>1</v>
@@ -8040,10 +8417,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H8" s="27" t="s">
         <v>1</v>
@@ -8064,25 +8441,25 @@
         <v>1</v>
       </c>
       <c r="N8" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O8" s="42" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="P8" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q8" s="42">
         <v>0</v>
       </c>
       <c r="R8" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S8" s="42">
         <v>0</v>
       </c>
       <c r="T8" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U8" s="42">
         <v>255</v>
@@ -8094,7 +8471,7 @@
         <v>1</v>
       </c>
       <c r="X8" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y8" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8172,10 +8549,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>1</v>
@@ -8184,10 +8561,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H9" s="27" t="s">
         <v>1</v>
@@ -8208,25 +8585,25 @@
         <v>1</v>
       </c>
       <c r="N9" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O9" s="42" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="P9" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q9" s="42">
         <v>200</v>
       </c>
       <c r="R9" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S9" s="42">
         <v>200</v>
       </c>
       <c r="T9" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U9" s="42">
         <v>200</v>
@@ -8238,7 +8615,7 @@
         <v>1</v>
       </c>
       <c r="X9" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y9" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8316,10 +8693,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>1</v>
@@ -8328,10 +8705,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H10" s="27" t="s">
         <v>1</v>
@@ -8352,25 +8729,25 @@
         <v>1</v>
       </c>
       <c r="N10" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O10" s="42" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="P10" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q10" s="42">
         <v>120</v>
       </c>
       <c r="R10" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S10" s="42">
         <v>120</v>
       </c>
       <c r="T10" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U10" s="42">
         <v>120</v>
@@ -8382,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y10" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8460,10 +8837,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>1</v>
@@ -8472,10 +8849,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H11" s="27" t="s">
         <v>1</v>
@@ -8496,25 +8873,25 @@
         <v>1</v>
       </c>
       <c r="N11" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O11" s="42" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="P11" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q11" s="42">
         <v>20</v>
       </c>
       <c r="R11" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S11" s="42">
         <v>20</v>
       </c>
       <c r="T11" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U11" s="42">
         <v>20</v>
@@ -8526,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="X11" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y11" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8604,10 +8981,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D12" s="27" t="s">
         <v>1</v>
@@ -8616,10 +8993,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>1</v>
@@ -8640,25 +9017,25 @@
         <v>1</v>
       </c>
       <c r="N12" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O12" s="42" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="P12" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q12" s="42">
         <v>150</v>
       </c>
       <c r="R12" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S12" s="42">
         <v>30</v>
       </c>
       <c r="T12" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U12" s="42">
         <v>10</v>
@@ -8670,7 +9047,7 @@
         <v>1</v>
       </c>
       <c r="X12" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y12" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8748,10 +9125,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D13" s="27" t="s">
         <v>1</v>
@@ -8760,10 +9137,10 @@
         <v>1</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H13" s="27" t="s">
         <v>1</v>
@@ -8784,25 +9161,25 @@
         <v>1</v>
       </c>
       <c r="N13" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O13" s="42" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="P13" s="39" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q13" s="42">
         <v>150</v>
       </c>
       <c r="R13" s="39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="S13" s="42">
         <v>40</v>
       </c>
       <c r="T13" s="39" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="U13" s="42">
         <v>10</v>
@@ -8814,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="X13" s="39" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Y13" s="42" t="str">
         <f t="shared" si="0"/>
@@ -8892,10 +9269,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>1</v>
@@ -8904,49 +9281,49 @@
         <v>1</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G14" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O14" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="H14" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="O14" s="42" t="s">
-        <v>324</v>
-      </c>
       <c r="P14" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q14" s="42">
         <v>150</v>
       </c>
       <c r="R14" s="39" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="S14" s="42">
         <v>50</v>
       </c>
       <c r="T14" s="39" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="U14" s="42">
         <v>10</v>
@@ -8958,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="39" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Y14" s="42" t="str">
         <f t="shared" si="0"/>
@@ -9036,10 +9413,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>1</v>
@@ -9048,49 +9425,49 @@
         <v>1</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G15" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O15" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="H15" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="O15" s="42" t="s">
-        <v>324</v>
-      </c>
       <c r="P15" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q15" s="42">
         <v>150</v>
       </c>
       <c r="R15" s="39" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="S15" s="42">
         <v>60</v>
       </c>
       <c r="T15" s="39" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="U15" s="42">
         <v>10</v>
@@ -9102,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="X15" s="39" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Y15" s="42" t="str">
         <f t="shared" si="0"/>
@@ -9180,10 +9557,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>1</v>
@@ -9210,16 +9587,16 @@
         <v>1</v>
       </c>
       <c r="L16" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="M16" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="N16" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="42" t="s">
+      <c r="O16" s="42" t="s">
         <v>134</v>
-      </c>
-      <c r="N16" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="O16" s="42" t="s">
-        <v>141</v>
       </c>
       <c r="P16" s="72" t="s">
         <v>1</v>
@@ -9253,16 +9630,16 @@
         <v>null</v>
       </c>
       <c r="Z16" s="39" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="AA16" s="42" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="AB16" s="39" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AC16" s="42" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AD16" s="39" t="s">
         <v>1</v>
@@ -9324,10 +9701,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>1</v>
@@ -9354,16 +9731,16 @@
         <v>1</v>
       </c>
       <c r="L17" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="M17" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="N17" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="N17" s="39" t="s">
-        <v>140</v>
-      </c>
       <c r="O17" s="42" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="P17" s="72" t="s">
         <v>1</v>
@@ -9397,16 +9774,16 @@
         <v>null</v>
       </c>
       <c r="Z17" s="39" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="AA17" s="42" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="AB17" s="39" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="AC17" s="42" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="AD17" s="39" t="s">
         <v>1</v>
@@ -9468,10 +9845,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D18" s="27" t="s">
         <v>1</v>
@@ -9504,10 +9881,10 @@
         <v>1</v>
       </c>
       <c r="N18" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O18" s="42" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="P18" s="72" t="s">
         <v>1</v>
@@ -9612,10 +9989,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>1</v>
@@ -9648,10 +10025,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O19" s="42" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="P19" s="72" t="s">
         <v>1</v>
@@ -9756,10 +10133,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D20" s="27" t="s">
         <v>1</v>
@@ -9792,10 +10169,10 @@
         <v>1</v>
       </c>
       <c r="N20" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O20" s="42" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="P20" s="72" t="s">
         <v>1</v>
@@ -9900,10 +10277,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>1</v>
@@ -9936,10 +10313,10 @@
         <v>1</v>
       </c>
       <c r="N21" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O21" s="42" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="P21" s="72" t="s">
         <v>1</v>
@@ -10044,22 +10421,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C22" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>122</v>
-      </c>
       <c r="G22" s="43" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H22" s="27" t="s">
         <v>1</v>
@@ -10080,25 +10457,25 @@
         <v>1</v>
       </c>
       <c r="N22" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O22" s="42" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="P22" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q22" s="42">
         <v>0</v>
       </c>
       <c r="R22" s="39" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="S22" s="42">
         <v>0</v>
       </c>
       <c r="T22" s="39" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="U22" s="42">
         <v>100</v>
@@ -10110,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="X22" s="39" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Y22" s="42" t="str">
         <f>IF(OR(X22="cor.rgb",X22="cor.cmy",X22="cor.rgba",X22="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q22,".",S22,".",U22,".",W22,""""), ".null",""), X22)</f>
@@ -10188,22 +10565,22 @@
         <v>23</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C23" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>122</v>
-      </c>
       <c r="G23" s="43" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H23" s="27" t="s">
         <v>1</v>
@@ -10224,25 +10601,25 @@
         <v>1</v>
       </c>
       <c r="N23" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O23" s="42" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="P23" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q23" s="42">
         <v>63</v>
       </c>
       <c r="R23" s="39" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="S23" s="42">
         <v>23</v>
       </c>
       <c r="T23" s="39" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="U23" s="42">
         <v>100</v>
@@ -10254,7 +10631,7 @@
         <v>1</v>
       </c>
       <c r="X23" s="39" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Y23" s="42" t="str">
         <f>IF(OR(X23="cor.rgb",X23="cor.cmy",X23="cor.rgba",X23="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q23,".",S23,".",U23,".",W23,""""), ".null",""), X23)</f>
@@ -10332,22 +10709,22 @@
         <v>24</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C24" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>122</v>
-      </c>
       <c r="G24" s="43" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H24" s="27" t="s">
         <v>1</v>
@@ -10368,25 +10745,25 @@
         <v>1</v>
       </c>
       <c r="N24" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O24" s="42" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="P24" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q24" s="42">
         <v>100</v>
       </c>
       <c r="R24" s="39" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="S24" s="42">
         <v>0</v>
       </c>
       <c r="T24" s="39" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="U24" s="42">
         <v>100</v>
@@ -10398,7 +10775,7 @@
         <v>1</v>
       </c>
       <c r="X24" s="39" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Y24" s="42" t="str">
         <f>IF(OR(X24="cor.rgb",X24="cor.cmy",X24="cor.rgba",X24="cor.cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",Q24,".",S24,".",U24,".",W24,""""), ".null",""), X24)</f>
@@ -10476,10 +10853,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>1</v>
@@ -10512,10 +10889,10 @@
         <v>1</v>
       </c>
       <c r="N25" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O25" s="42" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="P25" s="72" t="s">
         <v>1</v>
@@ -10619,16 +10996,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F26" s="27" t="s">
         <v>1</v>
@@ -10655,10 +11032,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O26" s="42" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="P26" s="72" t="s">
         <v>1</v>
@@ -10762,16 +11139,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F27" s="27" t="s">
         <v>1</v>
@@ -10798,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="N27" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O27" s="42" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P27" s="72" t="s">
         <v>1</v>
@@ -10905,16 +11282,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F28" s="27" t="s">
         <v>1</v>
@@ -10941,10 +11318,10 @@
         <v>1</v>
       </c>
       <c r="N28" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O28" s="42" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P28" s="72" t="s">
         <v>1</v>
@@ -11048,17 +11425,17 @@
         <v>29</v>
       </c>
       <c r="B29" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" s="46" t="s">
-        <v>160</v>
-      </c>
       <c r="F29" s="27" t="s">
         <v>1</v>
       </c>
@@ -11084,10 +11461,10 @@
         <v>1</v>
       </c>
       <c r="N29" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O29" s="42" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="P29" s="72" t="s">
         <v>1</v>
@@ -11191,16 +11568,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F30" s="27" t="s">
         <v>1</v>
@@ -11227,10 +11604,10 @@
         <v>1</v>
       </c>
       <c r="N30" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O30" s="42" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P30" s="72" t="s">
         <v>1</v>
@@ -11334,16 +11711,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F31" s="27" t="s">
         <v>1</v>
@@ -11370,10 +11747,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O31" s="42" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="P31" s="72" t="s">
         <v>1</v>
@@ -11477,16 +11854,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F32" s="27" t="s">
         <v>1</v>
@@ -11513,10 +11890,10 @@
         <v>1</v>
       </c>
       <c r="N32" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O32" s="42" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P32" s="72" t="s">
         <v>1</v>
@@ -11620,16 +11997,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F33" s="27" t="s">
         <v>1</v>
@@ -11656,10 +12033,10 @@
         <v>1</v>
       </c>
       <c r="N33" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O33" s="42" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="P33" s="72" t="s">
         <v>1</v>
@@ -11763,16 +12140,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F34" s="27" t="s">
         <v>1</v>
@@ -11799,10 +12176,10 @@
         <v>1</v>
       </c>
       <c r="N34" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O34" s="42" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="P34" s="72" t="s">
         <v>1</v>
@@ -11906,16 +12283,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F35" s="27" t="s">
         <v>1</v>
@@ -11942,10 +12319,10 @@
         <v>1</v>
       </c>
       <c r="N35" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O35" s="42" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="P35" s="72" t="s">
         <v>1</v>
@@ -12049,16 +12426,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>1</v>
@@ -12085,10 +12462,10 @@
         <v>1</v>
       </c>
       <c r="N36" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O36" s="42" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="P36" s="72" t="s">
         <v>1</v>
@@ -12192,16 +12569,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F37" s="27" t="s">
         <v>1</v>
@@ -12228,10 +12605,10 @@
         <v>1</v>
       </c>
       <c r="N37" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O37" s="42" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="P37" s="72" t="s">
         <v>1</v>
@@ -12335,16 +12712,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F38" s="27" t="s">
         <v>1</v>
@@ -12371,10 +12748,10 @@
         <v>1</v>
       </c>
       <c r="N38" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O38" s="42" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="P38" s="72" t="s">
         <v>1</v>
@@ -12478,16 +12855,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F39" s="27" t="s">
         <v>1</v>
@@ -12514,10 +12891,10 @@
         <v>1</v>
       </c>
       <c r="N39" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O39" s="42" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="P39" s="72" t="s">
         <v>1</v>
@@ -12621,16 +12998,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F40" s="27" t="s">
         <v>1</v>
@@ -12657,10 +13034,10 @@
         <v>1</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O40" s="42" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="P40" s="72" t="s">
         <v>1</v>
@@ -12764,16 +13141,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="20" t="s">
-        <v>175</v>
-      </c>
       <c r="D41" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F41" s="27" t="s">
         <v>1</v>
@@ -12800,10 +13177,10 @@
         <v>1</v>
       </c>
       <c r="N41" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O41" s="42" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="P41" s="72" t="s">
         <v>1</v>
@@ -12907,16 +13284,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F42" s="27" t="s">
         <v>1</v>
@@ -12943,10 +13320,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O42" s="42" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="P42" s="72" t="s">
         <v>1</v>
@@ -13050,16 +13427,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F43" s="27" t="s">
         <v>1</v>
@@ -13086,10 +13463,10 @@
         <v>1</v>
       </c>
       <c r="N43" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O43" s="42" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="P43" s="72" t="s">
         <v>1</v>
@@ -13193,16 +13570,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F44" s="27" t="s">
         <v>1</v>
@@ -13229,10 +13606,10 @@
         <v>1</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O44" s="42" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="P44" s="72" t="s">
         <v>1</v>
@@ -13336,16 +13713,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F45" s="27" t="s">
         <v>1</v>
@@ -13372,10 +13749,10 @@
         <v>1</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O45" s="42" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="P45" s="72" t="s">
         <v>1</v>
@@ -13479,16 +13856,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F46" s="27" t="s">
         <v>1</v>
@@ -13515,10 +13892,10 @@
         <v>1</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O46" s="42" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="P46" s="72" t="s">
         <v>1</v>
@@ -13622,16 +13999,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F47" s="27" t="s">
         <v>1</v>
@@ -13658,10 +14035,10 @@
         <v>1</v>
       </c>
       <c r="N47" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O47" s="42" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="P47" s="72" t="s">
         <v>1</v>
@@ -13765,16 +14142,16 @@
         <v>48</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F48" s="27" t="s">
         <v>1</v>
@@ -13801,10 +14178,10 @@
         <v>1</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O48" s="42" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="P48" s="72" t="s">
         <v>1</v>
@@ -13908,16 +14285,16 @@
         <v>49</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E49" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F49" s="27" t="s">
         <v>1</v>
@@ -13944,10 +14321,10 @@
         <v>1</v>
       </c>
       <c r="N49" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O49" s="42" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="P49" s="72" t="s">
         <v>1</v>
@@ -14051,16 +14428,16 @@
         <v>50</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F50" s="27" t="s">
         <v>1</v>
@@ -14087,10 +14464,10 @@
         <v>1</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O50" s="42" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="P50" s="72" t="s">
         <v>1</v>
@@ -14194,16 +14571,16 @@
         <v>51</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F51" s="27" t="s">
         <v>1</v>
@@ -14230,10 +14607,10 @@
         <v>1</v>
       </c>
       <c r="N51" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O51" s="42" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="P51" s="72" t="s">
         <v>1</v>
@@ -14337,16 +14714,16 @@
         <v>52</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F52" s="27" t="s">
         <v>1</v>
@@ -14361,22 +14738,22 @@
         <v>1</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K52" s="47" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="L52" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M52" s="47" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O52" s="49" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="P52" s="72" t="s">
         <v>1</v>
@@ -14421,10 +14798,10 @@
         <v>1</v>
       </c>
       <c r="AD52" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE52" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF52" s="39" t="s">
         <v>1</v>
@@ -14480,16 +14857,16 @@
         <v>53</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F53" s="27" t="s">
         <v>1</v>
@@ -14504,22 +14881,22 @@
         <v>1</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K53" s="47" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="L53" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M53" s="42" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="N53" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O53" s="49" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="P53" s="72" t="s">
         <v>1</v>
@@ -14564,10 +14941,10 @@
         <v>1</v>
       </c>
       <c r="AD53" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE53" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF53" s="39" t="s">
         <v>1</v>
@@ -14623,16 +15000,16 @@
         <v>54</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F54" s="27" t="s">
         <v>1</v>
@@ -14647,22 +15024,22 @@
         <v>1</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K54" s="47" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L54" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="M54" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="M54" s="47" t="s">
-        <v>189</v>
-      </c>
       <c r="N54" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O54" s="49" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P54" s="72" t="s">
         <v>1</v>
@@ -14707,10 +15084,10 @@
         <v>1</v>
       </c>
       <c r="AD54" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE54" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF54" s="39" t="s">
         <v>1</v>
@@ -14766,16 +15143,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E55" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F55" s="27" t="s">
         <v>1</v>
@@ -14790,22 +15167,22 @@
         <v>1</v>
       </c>
       <c r="J55" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K55" s="47" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L55" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M55" s="47" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N55" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O55" s="49" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="P55" s="72" t="s">
         <v>1</v>
@@ -14850,10 +15227,10 @@
         <v>1</v>
       </c>
       <c r="AD55" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE55" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF55" s="39" t="s">
         <v>1</v>
@@ -14909,16 +15286,16 @@
         <v>56</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F56" s="27" t="s">
         <v>1</v>
@@ -14933,70 +15310,70 @@
         <v>1</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K56" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="L56" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="M56" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="N56" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O56" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="P56" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="R56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="V56" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="W56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="X56" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE56" s="42" t="s">
         <v>218</v>
-      </c>
-      <c r="L56" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="M56" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="N56" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="O56" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="P56" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="R56" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T56" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="V56" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="W56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="X56" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB56" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="AE56" s="42" t="s">
-        <v>225</v>
       </c>
       <c r="AF56" s="39" t="s">
         <v>1</v>
@@ -15052,16 +15429,16 @@
         <v>57</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E57" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F57" s="27" t="s">
         <v>1</v>
@@ -15076,70 +15453,70 @@
         <v>1</v>
       </c>
       <c r="J57" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K57" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="L57" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="M57" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="N57" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O57" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="P57" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="R57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="V57" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="W57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="X57" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD57" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="L57" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="M57" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="N57" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="O57" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="P57" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="R57" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T57" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="V57" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="W57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="X57" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB57" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD57" s="39" t="s">
-        <v>226</v>
-      </c>
       <c r="AE57" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF57" s="39" t="s">
         <v>1</v>
@@ -15195,16 +15572,16 @@
         <v>58</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F58" s="27" t="s">
         <v>1</v>
@@ -15219,22 +15596,22 @@
         <v>1</v>
       </c>
       <c r="J58" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K58" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="K58" s="47" t="s">
-        <v>220</v>
-      </c>
       <c r="L58" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M58" s="47" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O58" s="49" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="P58" s="72" t="s">
         <v>1</v>
@@ -15279,10 +15656,10 @@
         <v>1</v>
       </c>
       <c r="AD58" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE58" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF58" s="39" t="s">
         <v>1</v>
@@ -15338,16 +15715,16 @@
         <v>59</v>
       </c>
       <c r="B59" s="45" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E59" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F59" s="27" t="s">
         <v>1</v>
@@ -15362,22 +15739,22 @@
         <v>1</v>
       </c>
       <c r="J59" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K59" s="47" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L59" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M59" s="47" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="N59" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O59" s="49" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="P59" s="72" t="s">
         <v>1</v>
@@ -15422,10 +15799,10 @@
         <v>1</v>
       </c>
       <c r="AD59" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE59" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF59" s="39" t="s">
         <v>1</v>
@@ -15481,16 +15858,16 @@
         <v>60</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F60" s="27" t="s">
         <v>1</v>
@@ -15505,22 +15882,22 @@
         <v>1</v>
       </c>
       <c r="J60" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K60" s="47" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L60" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M60" s="47" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N60" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O60" s="49" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P60" s="72" t="s">
         <v>1</v>
@@ -15565,10 +15942,10 @@
         <v>1</v>
       </c>
       <c r="AD60" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE60" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF60" s="39" t="s">
         <v>1</v>
@@ -15624,16 +16001,16 @@
         <v>61</v>
       </c>
       <c r="B61" s="45" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F61" s="27" t="s">
         <v>1</v>
@@ -15648,22 +16025,22 @@
         <v>1</v>
       </c>
       <c r="J61" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K61" s="47" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L61" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M61" s="47" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="N61" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O61" s="49" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P61" s="72" t="s">
         <v>1</v>
@@ -15708,10 +16085,10 @@
         <v>1</v>
       </c>
       <c r="AD61" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE61" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF61" s="39" t="s">
         <v>1</v>
@@ -15767,16 +16144,16 @@
         <v>62</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F62" s="27" t="s">
         <v>1</v>
@@ -15791,22 +16168,22 @@
         <v>1</v>
       </c>
       <c r="J62" s="39" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K62" s="47" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="L62" s="48" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M62" s="47" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O62" s="49" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="P62" s="72" t="s">
         <v>1</v>
@@ -15851,10 +16228,10 @@
         <v>1</v>
       </c>
       <c r="AD62" s="39" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AE62" s="42" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AF62" s="39" t="s">
         <v>1</v>
@@ -15910,10 +16287,10 @@
         <v>63</v>
       </c>
       <c r="B63" s="74" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C63" s="83" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D63" s="75" t="s">
         <v>1</v>
@@ -15946,10 +16323,10 @@
         <v>1</v>
       </c>
       <c r="N63" s="77" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O63" s="49" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="P63" s="72" t="s">
         <v>1</v>
@@ -16000,23 +16377,23 @@
         <v>1</v>
       </c>
       <c r="AF63" s="78" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AG63" s="49" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AH63" s="78" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AI63" s="49" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AJ63" s="79" t="str">
         <f t="shared" ref="AJ63:AJ67" si="2">IF(AK63="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="AK63" s="80" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AL63" s="27" t="s">
         <v>1</v>
@@ -16054,10 +16431,10 @@
         <v>64</v>
       </c>
       <c r="B64" s="74" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C64" s="83" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D64" s="75" t="s">
         <v>1</v>
@@ -16090,10 +16467,10 @@
         <v>1</v>
       </c>
       <c r="N64" s="77" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O64" s="49" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="P64" s="72" t="s">
         <v>1</v>
@@ -16144,23 +16521,23 @@
         <v>1</v>
       </c>
       <c r="AF64" s="78" t="s">
+        <v>388</v>
+      </c>
+      <c r="AG64" s="49" t="s">
+        <v>389</v>
+      </c>
+      <c r="AH64" s="78" t="s">
+        <v>390</v>
+      </c>
+      <c r="AI64" s="49" t="s">
         <v>395</v>
-      </c>
-      <c r="AG64" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="AH64" s="78" t="s">
-        <v>397</v>
-      </c>
-      <c r="AI64" s="49" t="s">
-        <v>402</v>
       </c>
       <c r="AJ64" s="79" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK64" s="80" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AL64" s="27" t="s">
         <v>1</v>
@@ -16198,10 +16575,10 @@
         <v>65</v>
       </c>
       <c r="B65" s="74" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C65" s="83" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D65" s="75" t="s">
         <v>1</v>
@@ -16234,10 +16611,10 @@
         <v>1</v>
       </c>
       <c r="N65" s="77" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O65" s="49" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="P65" s="72" t="s">
         <v>1</v>
@@ -16288,23 +16665,23 @@
         <v>1</v>
       </c>
       <c r="AF65" s="78" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AG65" s="49" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AH65" s="78" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AI65" s="49" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="AJ65" s="79" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK65" s="80" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="AL65" s="27" t="s">
         <v>1</v>
@@ -16342,10 +16719,10 @@
         <v>66</v>
       </c>
       <c r="B66" s="74" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C66" s="83" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D66" s="75" t="s">
         <v>1</v>
@@ -16378,10 +16755,10 @@
         <v>1</v>
       </c>
       <c r="N66" s="77" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O66" s="49" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="P66" s="72" t="s">
         <v>1</v>
@@ -16432,23 +16809,23 @@
         <v>1</v>
       </c>
       <c r="AF66" s="78" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AG66" s="49" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AH66" s="78" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AI66" s="49" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AJ66" s="79" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK66" s="80" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AL66" s="27" t="s">
         <v>1</v>
@@ -16486,10 +16863,10 @@
         <v>67</v>
       </c>
       <c r="B67" s="74" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C67" s="83" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D67" s="75" t="s">
         <v>1</v>
@@ -16522,10 +16899,10 @@
         <v>1</v>
       </c>
       <c r="N67" s="77" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O67" s="49" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="P67" s="72" t="s">
         <v>1</v>
@@ -16576,23 +16953,23 @@
         <v>1</v>
       </c>
       <c r="AF67" s="78" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AG67" s="49" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AH67" s="78" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AI67" s="49" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AJ67" s="79" t="str">
         <f t="shared" si="2"/>
         <v>método.revit</v>
       </c>
       <c r="AK67" s="80" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AL67" s="27" t="s">
         <v>1</v>
@@ -16631,50 +17008,50 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:I2 B3:I17 B18 B19:I19 B20:B21 B22:I62 A68:AS1048576 L1:Y15 Z1:AA17 AB1:AS62 AT1:AU1048576 A3:A67 T16:Y17 R16:S18 N22:Y31 Z22:AA62 L32:Y62 AL63:AS67 AV68:XFD1048576">
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B62 B68:B1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63:B67">
-    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:I18 AV1:XFD62 L16:Q17 N18:Q18 T18:AA18">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:I21 N19:AA21">
-    <cfRule type="cellIs" dxfId="14" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:I67">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K67">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18:M67">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P63:AE67">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16767,7 +17144,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16778,7 +17155,7 @@
         <v>37</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16789,7 +17166,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16800,7 +17177,7 @@
         <v>35</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16811,7 +17188,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16822,7 +17199,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16833,7 +17210,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16844,7 +17221,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -16855,22 +17232,22 @@
         <v>30</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C16" s="26" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C17" s="26" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
       <c r="C18" s="26" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="8.25" x14ac:dyDescent="0.15">
@@ -16905,7 +17282,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1 C7:C18">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
